--- a/Sheets/SEPEmployees.xlsx
+++ b/Sheets/SEPEmployees.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89CC2855-F883-41FE-B63B-92C30F8362E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D70378-8EF3-46A0-8C2D-0A11C39DC2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="623">
   <si>
     <t xml:space="preserve">Khaled Mohamed Helmy Mohamed Yousry Abd Rabo </t>
   </si>
@@ -2035,6 +2035,9 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>NationalID</t>
   </si>
 </sst>
 </file>
@@ -3556,12 +3559,45 @@
     <xf numFmtId="0" fontId="5" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="25" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3571,42 +3607,162 @@
     <xf numFmtId="165" fontId="25" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3651,159 +3807,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4376,7 +4379,7 @@
         <v>265</v>
       </c>
       <c r="M1" s="171" t="s">
-        <v>67</v>
+        <v>622</v>
       </c>
       <c r="N1" s="173"/>
       <c r="O1" s="174" t="s">
@@ -4563,11 +4566,11 @@
         <v>69</v>
       </c>
       <c r="Z3" s="100">
-        <f ca="1">DATEDIF(R3,TODAY(),"Y")</f>
+        <f t="shared" ref="Z3:Z46" ca="1" si="0">DATEDIF(R3,TODAY(),"Y")</f>
         <v>18</v>
       </c>
       <c r="AA3" s="100">
-        <f ca="1">DATEDIF(R3,TODAY(),"Ym")</f>
+        <f t="shared" ref="AA3:AA46" ca="1" si="1">DATEDIF(R3,TODAY(),"Ym")</f>
         <v>11</v>
       </c>
       <c r="AB3" s="97" t="s">
@@ -4657,11 +4660,11 @@
         <v>69</v>
       </c>
       <c r="Z4" s="100">
-        <f ca="1">DATEDIF(R4,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
       <c r="AA4" s="100">
-        <f ca="1">DATEDIF(R4,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB4" s="97" t="s">
@@ -4751,11 +4754,11 @@
         <v>69</v>
       </c>
       <c r="Z5" s="100">
-        <f ca="1">DATEDIF(R5,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="AA5" s="100">
-        <f ca="1">DATEDIF(R5,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="AB5" s="97">
@@ -4845,11 +4848,11 @@
         <v>69</v>
       </c>
       <c r="Z6" s="100">
-        <f ca="1">DATEDIF(R6,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
       <c r="AA6" s="100">
-        <f ca="1">DATEDIF(R6,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB6" s="97">
@@ -4939,11 +4942,11 @@
         <v>69</v>
       </c>
       <c r="Z7" s="100">
-        <f ca="1">DATEDIF(R7,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
       <c r="AA7" s="100">
-        <f ca="1">DATEDIF(R7,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB7" s="97">
@@ -5033,11 +5036,11 @@
         <v>69</v>
       </c>
       <c r="Z8" s="100">
-        <f ca="1">DATEDIF(R8,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="AA8" s="100">
-        <f ca="1">DATEDIF(R8,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
       <c r="AB8" s="97">
@@ -5127,11 +5130,11 @@
         <v>69</v>
       </c>
       <c r="Z9" s="100">
-        <f ca="1">DATEDIF(R9,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
       <c r="AA9" s="100">
-        <f ca="1">DATEDIF(R9,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="AB9" s="97">
@@ -5221,11 +5224,11 @@
         <v>69</v>
       </c>
       <c r="Z10" s="100">
-        <f ca="1">DATEDIF(R10,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
       <c r="AA10" s="100">
-        <f ca="1">DATEDIF(R10,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB10" s="97">
@@ -5315,11 +5318,11 @@
         <v>69</v>
       </c>
       <c r="Z11" s="100">
-        <f ca="1">DATEDIF(R11,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
       <c r="AA11" s="100">
-        <f ca="1">DATEDIF(R11,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="AB11" s="97">
@@ -5410,11 +5413,11 @@
         <v>46203</v>
       </c>
       <c r="Z12" s="100">
-        <f ca="1">DATEDIF(R12,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="AA12" s="100">
-        <f ca="1">DATEDIF(R12,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB12" s="97">
@@ -5504,11 +5507,11 @@
         <v>69</v>
       </c>
       <c r="Z13" s="100">
-        <f ca="1">DATEDIF(R13,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="AA13" s="100">
-        <f ca="1">DATEDIF(R13,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
       <c r="AB13" s="97">
@@ -5598,11 +5601,11 @@
         <v>69</v>
       </c>
       <c r="Z14" s="128">
-        <f ca="1">DATEDIF(R14,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="AA14" s="128">
-        <f ca="1">DATEDIF(R14,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB14" s="127">
@@ -5690,11 +5693,11 @@
       </c>
       <c r="Y15" s="140"/>
       <c r="Z15" s="128">
-        <f ca="1">DATEDIF(R15,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="AA15" s="128">
-        <f ca="1">DATEDIF(R15,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="AB15" s="127" t="s">
@@ -5782,11 +5785,11 @@
       </c>
       <c r="Y16" s="140"/>
       <c r="Z16" s="128">
-        <f ca="1">DATEDIF(R16,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="AA16" s="128">
-        <f ca="1">DATEDIF(R16,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB16" s="127" t="s">
@@ -5876,11 +5879,11 @@
         <v>69</v>
       </c>
       <c r="Z17" s="128">
-        <f ca="1">DATEDIF(R17,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="AA17" s="128">
-        <f ca="1">DATEDIF(R17,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="AB17" s="127" t="s">
@@ -5970,11 +5973,11 @@
         <v>69</v>
       </c>
       <c r="Z18" s="100">
-        <f ca="1">DATEDIF(R18,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="AA18" s="100">
-        <f ca="1">DATEDIF(R18,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB18" s="97" t="s">
@@ -6064,11 +6067,11 @@
         <v>69</v>
       </c>
       <c r="Z19" s="128">
-        <f ca="1">DATEDIF(R19,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="AA19" s="128">
-        <f ca="1">DATEDIF(R19,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
       <c r="AB19" s="127" t="s">
@@ -6158,11 +6161,11 @@
         <v>69</v>
       </c>
       <c r="Z20" s="100">
-        <f ca="1">DATEDIF(R20,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="AA20" s="100">
-        <f ca="1">DATEDIF(R20,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB20" s="97">
@@ -6252,11 +6255,11 @@
         <v>69</v>
       </c>
       <c r="Z21" s="100">
-        <f ca="1">DATEDIF(R21,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="AA21" s="100">
-        <f ca="1">DATEDIF(R21,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB21" s="97" t="s">
@@ -6346,11 +6349,11 @@
         <v>69</v>
       </c>
       <c r="Z22" s="128">
-        <f ca="1">DATEDIF(R22,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="AA22" s="128">
-        <f ca="1">DATEDIF(R22,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
       <c r="AB22" s="127" t="s">
@@ -6440,11 +6443,11 @@
         <v>69</v>
       </c>
       <c r="Z23" s="128">
-        <f ca="1">DATEDIF(R23,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="AA23" s="128">
-        <f ca="1">DATEDIF(R23,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>8</v>
       </c>
       <c r="AB23" s="127" t="s">
@@ -6534,11 +6537,11 @@
         <v>69</v>
       </c>
       <c r="Z24" s="100">
-        <f ca="1">DATEDIF(R24,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="AA24" s="100">
-        <f ca="1">DATEDIF(R24,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="AB24" s="97" t="s">
@@ -6628,11 +6631,11 @@
         <v>69</v>
       </c>
       <c r="Z25" s="100">
-        <f ca="1">DATEDIF(R25,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="AA25" s="100">
-        <f ca="1">DATEDIF(R25,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
       <c r="AB25" s="97" t="s">
@@ -6722,11 +6725,11 @@
         <v>69</v>
       </c>
       <c r="Z26" s="100">
-        <f ca="1">DATEDIF(R26,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="AA26" s="100">
-        <f ca="1">DATEDIF(R26,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="AB26" s="97" t="s">
@@ -6817,11 +6820,11 @@
         <v>46219</v>
       </c>
       <c r="Z27" s="100">
-        <f ca="1">DATEDIF(R27,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
       <c r="AA27" s="100">
-        <f ca="1">DATEDIF(R27,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB27" s="97">
@@ -6912,11 +6915,11 @@
         <v>46042</v>
       </c>
       <c r="Z28" s="100">
-        <f ca="1">DATEDIF(R28,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
       <c r="AA28" s="100">
-        <f ca="1">DATEDIF(R28,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB28" s="97">
@@ -7007,11 +7010,11 @@
         <v>46126</v>
       </c>
       <c r="Z29" s="100">
-        <f ca="1">DATEDIF(R29,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
       <c r="AA29" s="100">
-        <f ca="1">DATEDIF(R29,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="AB29" s="97">
@@ -7101,11 +7104,11 @@
         <v>45275</v>
       </c>
       <c r="Z30" s="128">
-        <f ca="1">DATEDIF(R30,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="AA30" s="128">
-        <f ca="1">DATEDIF(R30,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="AB30" s="127" t="s">
@@ -7196,11 +7199,11 @@
         <v>46162</v>
       </c>
       <c r="Z31" s="100">
-        <f ca="1">DATEDIF(R31,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
       <c r="AA31" s="100">
-        <f ca="1">DATEDIF(R31,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
       <c r="AB31" s="97">
@@ -7291,11 +7294,11 @@
         <v>46090</v>
       </c>
       <c r="Z32" s="100">
-        <f ca="1">DATEDIF(R32,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="AA32" s="100">
-        <f ca="1">DATEDIF(R32,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
       <c r="AB32" s="97" t="s">
@@ -7386,11 +7389,11 @@
         <v>46053</v>
       </c>
       <c r="Z33" s="128">
-        <f ca="1">DATEDIF(R33,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
       <c r="AA33" s="128">
-        <f ca="1">DATEDIF(R33,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="AB33" s="127" t="s">
@@ -7481,11 +7484,11 @@
         <v>46314</v>
       </c>
       <c r="Z34" s="100">
-        <f ca="1">DATEDIF(R34,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
       <c r="AA34" s="100">
-        <f ca="1">DATEDIF(R34,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="AB34" s="97">
@@ -7576,11 +7579,11 @@
         <v>46049</v>
       </c>
       <c r="Z35" s="100">
-        <f ca="1">DATEDIF(R35,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
       <c r="AA35" s="100">
-        <f ca="1">DATEDIF(R35,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB35" s="97">
@@ -7671,11 +7674,11 @@
         <v>46190</v>
       </c>
       <c r="Z36" s="100">
-        <f ca="1">DATEDIF(R36,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="AA36" s="100">
-        <f ca="1">DATEDIF(R36,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="AB36" s="97">
@@ -7764,11 +7767,11 @@
         <v>46022</v>
       </c>
       <c r="Z37" s="100">
-        <f ca="1">DATEDIF(R37,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
       <c r="AA37" s="100">
-        <f ca="1">DATEDIF(R37,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB37" s="97">
@@ -7859,11 +7862,11 @@
         <v>46203</v>
       </c>
       <c r="Z38" s="100">
-        <f ca="1">DATEDIF(R38,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
       <c r="AA38" s="100">
-        <f ca="1">DATEDIF(R38,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB38" s="97">
@@ -7954,11 +7957,11 @@
         <v>46217</v>
       </c>
       <c r="Z39" s="100">
-        <f ca="1">DATEDIF(R39,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
       <c r="AA39" s="100">
-        <f ca="1">DATEDIF(R39,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB39" s="97" t="s">
@@ -8049,11 +8052,11 @@
         <v>46340</v>
       </c>
       <c r="Z40" s="100">
-        <f ca="1">DATEDIF(R40,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
       <c r="AA40" s="100">
-        <f ca="1">DATEDIF(R40,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
       <c r="AB40" s="97" t="s">
@@ -8144,11 +8147,11 @@
         <v>46202</v>
       </c>
       <c r="Z41" s="100">
-        <f ca="1">DATEDIF(R41,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
       <c r="AA41" s="100">
-        <f ca="1">DATEDIF(R41,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
       <c r="AB41" s="97" t="s">
@@ -8239,11 +8242,11 @@
         <v>46345</v>
       </c>
       <c r="Z42" s="100">
-        <f ca="1">DATEDIF(R42,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
       <c r="AA42" s="100">
-        <f ca="1">DATEDIF(R42,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
       <c r="AB42" s="97">
@@ -8333,11 +8336,11 @@
         <v>69</v>
       </c>
       <c r="Z43" s="128">
-        <f ca="1">DATEDIF(R43,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
       <c r="AA43" s="128">
-        <f ca="1">DATEDIF(R43,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="AB43" s="127" t="s">
@@ -8428,11 +8431,11 @@
         <v>46222</v>
       </c>
       <c r="Z44" s="100">
-        <f ca="1">DATEDIF(R44,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="AA44" s="100">
-        <f ca="1">DATEDIF(R44,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>11</v>
       </c>
       <c r="AB44" s="97" t="s">
@@ -8523,11 +8526,11 @@
         <v>46084</v>
       </c>
       <c r="Z45" s="100">
-        <f ca="1">DATEDIF(R45,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="AA45" s="100">
-        <f ca="1">DATEDIF(R45,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="AB45" s="97" t="s">
@@ -8618,11 +8621,11 @@
         <v>46006</v>
       </c>
       <c r="Z46" s="100">
-        <f ca="1">DATEDIF(R46,TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="AA46" s="100">
-        <f ca="1">DATEDIF(R46,TODAY(),"Ym")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="AB46" s="97" t="s">
@@ -9243,14 +9246,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="189" t="s">
+      <c r="B1" s="183"/>
+      <c r="C1" s="184" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="188" t="s">
+      <c r="D1" s="183" t="s">
         <v>260</v>
       </c>
     </row>
@@ -9261,17 +9264,17 @@
       <c r="B2" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="C2" s="189"/>
-      <c r="D2" s="188"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="183"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="187" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="191"/>
+      <c r="C3" s="188"/>
       <c r="D3" s="53">
         <v>46219</v>
       </c>
@@ -9442,10 +9445,10 @@
       <c r="A18" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="183" t="s">
+      <c r="B18" s="185" t="s">
         <v>379</v>
       </c>
-      <c r="C18" s="184"/>
+      <c r="C18" s="186"/>
       <c r="D18" s="53">
         <v>46042</v>
       </c>
@@ -9616,10 +9619,10 @@
       <c r="A33" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="B33" s="183" t="s">
+      <c r="B33" s="185" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="184"/>
+      <c r="C33" s="186"/>
       <c r="D33" s="53">
         <v>46126</v>
       </c>
@@ -9748,21 +9751,21 @@
       <c r="A45" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="B45" s="192" t="s">
+      <c r="B45" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="193"/>
+      <c r="C45" s="190"/>
       <c r="D45" s="66">
         <v>45274</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="196" t="s">
+      <c r="A46" s="193" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="197"/>
-      <c r="C46" s="197"/>
-      <c r="D46" s="198"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="195"/>
     </row>
     <row r="47" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="67">
@@ -9830,10 +9833,10 @@
       <c r="A52" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="B52" s="183" t="s">
+      <c r="B52" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="184"/>
+      <c r="C52" s="186"/>
       <c r="D52" s="53">
         <v>46162</v>
       </c>
@@ -9964,10 +9967,10 @@
       <c r="A64" s="51" t="s">
         <v>300</v>
       </c>
-      <c r="B64" s="183" t="s">
+      <c r="B64" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C64" s="184"/>
+      <c r="C64" s="186"/>
       <c r="D64" s="53">
         <v>46090</v>
       </c>
@@ -10078,10 +10081,10 @@
       <c r="A74" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="183" t="s">
+      <c r="B74" s="185" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="184"/>
+      <c r="C74" s="186"/>
       <c r="D74" s="53">
         <v>46053</v>
       </c>
@@ -10164,10 +10167,10 @@
       <c r="A82" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="194" t="s">
+      <c r="B82" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="C82" s="195"/>
+      <c r="C82" s="192"/>
       <c r="D82" s="53">
         <v>46314</v>
       </c>
@@ -10326,10 +10329,10 @@
       <c r="A96" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="B96" s="183" t="s">
+      <c r="B96" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C96" s="184"/>
+      <c r="C96" s="186"/>
       <c r="D96" s="53">
         <v>46049</v>
       </c>
@@ -10472,10 +10475,10 @@
       <c r="A109" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="183" t="s">
+      <c r="B109" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="184"/>
+      <c r="C109" s="186"/>
       <c r="D109" s="53">
         <v>46190</v>
       </c>
@@ -10554,10 +10557,10 @@
       <c r="A116" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="B116" s="183" t="s">
+      <c r="B116" s="185" t="s">
         <v>8</v>
       </c>
-      <c r="C116" s="184"/>
+      <c r="C116" s="186"/>
       <c r="D116" s="53">
         <v>46022</v>
       </c>
@@ -10740,10 +10743,10 @@
       <c r="A132" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="B132" s="183" t="s">
+      <c r="B132" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="184"/>
+      <c r="C132" s="186"/>
       <c r="D132" s="53">
         <v>46203</v>
       </c>
@@ -10902,10 +10905,10 @@
       <c r="A146" s="51" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="183" t="s">
+      <c r="B146" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="C146" s="184"/>
+      <c r="C146" s="186"/>
       <c r="D146" s="53">
         <v>46217</v>
       </c>
@@ -11088,10 +11091,10 @@
       <c r="A162" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="B162" s="183" t="s">
+      <c r="B162" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="184"/>
+      <c r="C162" s="186"/>
       <c r="D162" s="53">
         <v>46340</v>
       </c>
@@ -11322,10 +11325,10 @@
       <c r="A182" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="B182" s="183" t="s">
+      <c r="B182" s="185" t="s">
         <v>11</v>
       </c>
-      <c r="C182" s="184"/>
+      <c r="C182" s="186"/>
       <c r="D182" s="53">
         <v>46202</v>
       </c>
@@ -11508,10 +11511,10 @@
       <c r="A198" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="B198" s="183" t="s">
+      <c r="B198" s="185" t="s">
         <v>12</v>
       </c>
-      <c r="C198" s="184"/>
+      <c r="C198" s="186"/>
       <c r="D198" s="53">
         <v>46345</v>
       </c>
@@ -11648,10 +11651,10 @@
       <c r="A210" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="B210" s="183" t="s">
+      <c r="B210" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="184"/>
+      <c r="C210" s="186"/>
       <c r="D210" s="53">
         <v>46222</v>
       </c>
@@ -11750,10 +11753,10 @@
       <c r="A219" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="B219" s="183" t="s">
+      <c r="B219" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="C219" s="184"/>
+      <c r="C219" s="186"/>
       <c r="D219" s="53">
         <v>46084</v>
       </c>
@@ -11806,10 +11809,10 @@
       <c r="A224" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="B224" s="183" t="s">
+      <c r="B224" s="185" t="s">
         <v>164</v>
       </c>
-      <c r="C224" s="184"/>
+      <c r="C224" s="186"/>
       <c r="D224" s="53">
         <v>46006</v>
       </c>
@@ -11866,10 +11869,10 @@
       <c r="A230" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="B230" s="183" t="s">
+      <c r="B230" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="C230" s="184"/>
+      <c r="C230" s="186"/>
       <c r="D230" s="53">
         <v>46203</v>
       </c>
@@ -11956,21 +11959,21 @@
       <c r="A238" s="62" t="s">
         <v>472</v>
       </c>
-      <c r="B238" s="183" t="s">
+      <c r="B238" s="185" t="s">
         <v>473</v>
       </c>
-      <c r="C238" s="184"/>
+      <c r="C238" s="186"/>
       <c r="D238" s="53">
         <v>45460</v>
       </c>
     </row>
     <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="185" t="s">
+      <c r="A239" s="196" t="s">
         <v>385</v>
       </c>
-      <c r="B239" s="186"/>
-      <c r="C239" s="186"/>
-      <c r="D239" s="187"/>
+      <c r="B239" s="197"/>
+      <c r="C239" s="197"/>
+      <c r="D239" s="198"/>
     </row>
     <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="48">
@@ -11990,21 +11993,21 @@
       <c r="A241" s="62" t="s">
         <v>505</v>
       </c>
-      <c r="B241" s="183" t="s">
+      <c r="B241" s="185" t="s">
         <v>510</v>
       </c>
-      <c r="C241" s="184"/>
+      <c r="C241" s="186"/>
       <c r="D241" s="53">
         <v>45579</v>
       </c>
     </row>
     <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="185" t="s">
+      <c r="A242" s="196" t="s">
         <v>385</v>
       </c>
-      <c r="B242" s="186"/>
-      <c r="C242" s="186"/>
-      <c r="D242" s="187"/>
+      <c r="B242" s="197"/>
+      <c r="C242" s="197"/>
+      <c r="D242" s="198"/>
     </row>
     <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="48">
@@ -12024,10 +12027,10 @@
       <c r="A244" s="62" t="s">
         <v>514</v>
       </c>
-      <c r="B244" s="183" t="s">
+      <c r="B244" s="185" t="s">
         <v>524</v>
       </c>
-      <c r="C244" s="184"/>
+      <c r="C244" s="186"/>
       <c r="D244" s="53">
         <v>46167</v>
       </c>
@@ -12080,10 +12083,10 @@
       <c r="A249" s="62" t="s">
         <v>527</v>
       </c>
-      <c r="B249" s="183" t="s">
+      <c r="B249" s="185" t="s">
         <v>529</v>
       </c>
-      <c r="C249" s="184"/>
+      <c r="C249" s="186"/>
       <c r="D249" s="53">
         <v>46234</v>
       </c>
@@ -12136,10 +12139,10 @@
       <c r="A254" s="62" t="s">
         <v>611</v>
       </c>
-      <c r="B254" s="183" t="s">
+      <c r="B254" s="185" t="s">
         <v>612</v>
       </c>
-      <c r="C254" s="184"/>
+      <c r="C254" s="186"/>
       <c r="D254" s="53">
         <v>46194</v>
       </c>
@@ -12166,21 +12169,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B109:C109"/>
     <mergeCell ref="B254:C254"/>
     <mergeCell ref="B146:C146"/>
     <mergeCell ref="B162:C162"/>
@@ -12197,6 +12185,21 @@
     <mergeCell ref="A239:D239"/>
     <mergeCell ref="A242:D242"/>
     <mergeCell ref="B249:C249"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B109:C109"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="timePeriod" dxfId="24" priority="34" timePeriod="nextWeek">
@@ -16943,49 +16946,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="251" t="s">
         <v>373</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="202"/>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="252"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
+      <c r="I1" s="252"/>
+      <c r="J1" s="252"/>
+      <c r="K1" s="252"/>
+      <c r="L1" s="252"/>
+      <c r="M1" s="252"/>
+      <c r="N1" s="252"/>
+      <c r="O1" s="253"/>
     </row>
     <row r="2" spans="1:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="254" t="s">
         <v>497</v>
       </c>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="205" t="s">
+      <c r="C2" s="254"/>
+      <c r="D2" s="254"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="256" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="208" t="str">
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="259" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,2,)</f>
         <v>Lawyer</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="M2" s="209"/>
-      <c r="N2" s="209"/>
-      <c r="O2" s="210"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="261"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37"/>
@@ -17005,18 +17008,18 @@
       <c r="O3" s="42"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="211" t="s">
+      <c r="A4" s="262" t="s">
         <v>461</v>
       </c>
-      <c r="B4" s="212"/>
+      <c r="B4" s="263"/>
       <c r="C4" s="34"/>
       <c r="D4" s="43"/>
       <c r="E4" s="43"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
       <c r="M4" s="35"/>
@@ -17024,136 +17027,136 @@
       <c r="O4" s="44"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="215" t="s">
+      <c r="A5" s="222" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217" t="str">
+      <c r="B5" s="223"/>
+      <c r="C5" s="245" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,3,)</f>
         <v>Hussien Sherif Mohamed Monier Amer</v>
       </c>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="218"/>
-      <c r="H5" s="218"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="218"/>
-      <c r="K5" s="218"/>
-      <c r="L5" s="218"/>
-      <c r="M5" s="218"/>
-      <c r="N5" s="218"/>
-      <c r="O5" s="219"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="M5" s="246"/>
+      <c r="N5" s="246"/>
+      <c r="O5" s="247"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="220" t="s">
+      <c r="A6" s="229" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="221"/>
-      <c r="C6" s="222" t="str">
+      <c r="B6" s="230"/>
+      <c r="C6" s="248" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,17,)</f>
         <v>-</v>
       </c>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="223"/>
-      <c r="O6" s="224"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="249"/>
+      <c r="H6" s="249"/>
+      <c r="I6" s="249"/>
+      <c r="J6" s="249"/>
+      <c r="K6" s="249"/>
+      <c r="L6" s="249"/>
+      <c r="M6" s="249"/>
+      <c r="N6" s="249"/>
+      <c r="O6" s="250"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="220" t="s">
+      <c r="A7" s="229" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="221"/>
-      <c r="C7" s="225" t="str">
+      <c r="B7" s="230"/>
+      <c r="C7" s="241" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,4,)</f>
         <v>حسين شريف محمد منير عامر</v>
       </c>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="227"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="232"/>
+      <c r="O7" s="233"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="220" t="s">
+      <c r="A8" s="229" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="221"/>
-      <c r="C8" s="225" t="str">
+      <c r="B8" s="230"/>
+      <c r="C8" s="241" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,5,)</f>
         <v xml:space="preserve">Associate </v>
       </c>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="226"/>
-      <c r="O8" s="227"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="233"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="220" t="s">
+      <c r="A9" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="221"/>
-      <c r="C9" s="228" t="str">
+      <c r="B9" s="230"/>
+      <c r="C9" s="242" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,6,)</f>
         <v>Banking &amp; Procedures</v>
       </c>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="230"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="244"/>
     </row>
     <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="217" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="232"/>
-      <c r="C10" s="233">
+      <c r="B10" s="218"/>
+      <c r="C10" s="206">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,22,)</f>
         <v>406</v>
       </c>
-      <c r="D10" s="233"/>
-      <c r="E10" s="233"/>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="234"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
+      <c r="J10" s="206"/>
+      <c r="K10" s="206"/>
+      <c r="L10" s="206"/>
+      <c r="M10" s="206"/>
+      <c r="N10" s="206"/>
+      <c r="O10" s="207"/>
     </row>
     <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33"/>
@@ -17173,111 +17176,111 @@
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="242" t="s">
+      <c r="A12" s="208" t="s">
         <v>454</v>
       </c>
-      <c r="B12" s="243"/>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="244"/>
-      <c r="I12" s="244"/>
-      <c r="J12" s="244"/>
-      <c r="K12" s="244"/>
-      <c r="L12" s="244"/>
-      <c r="M12" s="244"/>
-      <c r="N12" s="244"/>
-      <c r="O12" s="245"/>
+      <c r="B12" s="209"/>
+      <c r="C12" s="238"/>
+      <c r="D12" s="238"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="238"/>
+      <c r="G12" s="238"/>
+      <c r="H12" s="238"/>
+      <c r="I12" s="238"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="238"/>
+      <c r="L12" s="238"/>
+      <c r="M12" s="238"/>
+      <c r="N12" s="238"/>
+      <c r="O12" s="239"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="215" t="s">
+      <c r="A13" s="222" t="s">
         <v>455</v>
       </c>
-      <c r="B13" s="216"/>
-      <c r="C13" s="246">
+      <c r="B13" s="223"/>
+      <c r="C13" s="240">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,7,)</f>
         <v>35383</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
-      <c r="F13" s="247"/>
-      <c r="G13" s="247"/>
-      <c r="H13" s="247"/>
-      <c r="I13" s="247"/>
-      <c r="J13" s="247"/>
-      <c r="K13" s="247"/>
-      <c r="L13" s="247"/>
-      <c r="M13" s="247"/>
-      <c r="N13" s="247"/>
-      <c r="O13" s="248"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
+      <c r="M13" s="225"/>
+      <c r="N13" s="225"/>
+      <c r="O13" s="226"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="220" t="s">
+      <c r="A14" s="229" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="221"/>
-      <c r="C14" s="225" t="str">
+      <c r="B14" s="230"/>
+      <c r="C14" s="241" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,8,)</f>
         <v>Master of Laws</v>
       </c>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="226"/>
-      <c r="I14" s="226"/>
-      <c r="J14" s="226"/>
-      <c r="K14" s="226"/>
-      <c r="L14" s="226"/>
-      <c r="M14" s="226"/>
-      <c r="N14" s="226"/>
-      <c r="O14" s="227"/>
+      <c r="D14" s="232"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="232"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="232"/>
+      <c r="K14" s="232"/>
+      <c r="L14" s="232"/>
+      <c r="M14" s="232"/>
+      <c r="N14" s="232"/>
+      <c r="O14" s="233"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="238" t="s">
+      <c r="A15" s="214" t="s">
         <v>456</v>
       </c>
-      <c r="B15" s="239"/>
-      <c r="C15" s="249" t="str">
+      <c r="B15" s="215"/>
+      <c r="C15" s="216" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,9,)</f>
         <v>Professional Legal Practice</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="E15" s="240"/>
-      <c r="F15" s="240"/>
-      <c r="G15" s="240"/>
-      <c r="H15" s="240"/>
-      <c r="I15" s="240"/>
-      <c r="J15" s="240"/>
-      <c r="K15" s="240"/>
-      <c r="L15" s="240"/>
-      <c r="M15" s="240"/>
-      <c r="N15" s="240"/>
-      <c r="O15" s="241"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="202"/>
+      <c r="G15" s="202"/>
+      <c r="H15" s="202"/>
+      <c r="I15" s="202"/>
+      <c r="J15" s="202"/>
+      <c r="K15" s="202"/>
+      <c r="L15" s="202"/>
+      <c r="M15" s="202"/>
+      <c r="N15" s="202"/>
+      <c r="O15" s="203"/>
     </row>
     <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="231" t="s">
+      <c r="A16" s="217" t="s">
         <v>463</v>
       </c>
-      <c r="B16" s="232"/>
-      <c r="C16" s="250" t="str">
+      <c r="B16" s="218"/>
+      <c r="C16" s="219" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,10,)</f>
         <v>University of Law</v>
       </c>
-      <c r="D16" s="251"/>
-      <c r="E16" s="251"/>
-      <c r="F16" s="251"/>
-      <c r="G16" s="251"/>
-      <c r="H16" s="251"/>
-      <c r="I16" s="251"/>
-      <c r="J16" s="251"/>
-      <c r="K16" s="251"/>
-      <c r="L16" s="251"/>
-      <c r="M16" s="251"/>
-      <c r="N16" s="251"/>
-      <c r="O16" s="252"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
+      <c r="F16" s="220"/>
+      <c r="G16" s="220"/>
+      <c r="H16" s="220"/>
+      <c r="I16" s="220"/>
+      <c r="J16" s="220"/>
+      <c r="K16" s="220"/>
+      <c r="L16" s="220"/>
+      <c r="M16" s="220"/>
+      <c r="N16" s="220"/>
+      <c r="O16" s="221"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="33"/>
@@ -17297,10 +17300,10 @@
       <c r="O17" s="36"/>
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="242" t="s">
+      <c r="A18" s="208" t="s">
         <v>462</v>
       </c>
-      <c r="B18" s="243"/>
+      <c r="B18" s="209"/>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
@@ -17316,10 +17319,10 @@
       <c r="O18" s="36"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="215" t="s">
+      <c r="A19" s="222" t="s">
         <v>376</v>
       </c>
-      <c r="B19" s="216"/>
+      <c r="B19" s="223"/>
       <c r="C19" s="235" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,12,)</f>
         <v>-</v>
@@ -17338,92 +17341,92 @@
       <c r="O19" s="237"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="238" t="s">
+      <c r="A20" s="214" t="s">
         <v>457</v>
       </c>
-      <c r="B20" s="239"/>
-      <c r="C20" s="240">
+      <c r="B20" s="215"/>
+      <c r="C20" s="202">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,14,)</f>
         <v>47469</v>
       </c>
-      <c r="D20" s="240"/>
-      <c r="E20" s="240"/>
-      <c r="F20" s="240"/>
-      <c r="G20" s="240"/>
-      <c r="H20" s="240"/>
-      <c r="I20" s="240"/>
-      <c r="J20" s="240"/>
-      <c r="K20" s="240"/>
-      <c r="L20" s="240"/>
-      <c r="M20" s="240"/>
-      <c r="N20" s="240"/>
-      <c r="O20" s="241"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="202"/>
+      <c r="F20" s="202"/>
+      <c r="G20" s="202"/>
+      <c r="H20" s="202"/>
+      <c r="I20" s="202"/>
+      <c r="J20" s="202"/>
+      <c r="K20" s="202"/>
+      <c r="L20" s="202"/>
+      <c r="M20" s="202"/>
+      <c r="N20" s="202"/>
+      <c r="O20" s="203"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="238" t="s">
+      <c r="A21" s="214" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="239"/>
-      <c r="C21" s="249">
+      <c r="B21" s="215"/>
+      <c r="C21" s="216">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,15,)</f>
         <v>710391</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="240"/>
-      <c r="F21" s="240"/>
-      <c r="G21" s="240"/>
-      <c r="H21" s="240"/>
-      <c r="I21" s="240"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="240"/>
-      <c r="L21" s="240"/>
-      <c r="M21" s="240"/>
-      <c r="N21" s="240"/>
-      <c r="O21" s="241"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="202"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="202"/>
+      <c r="I21" s="202"/>
+      <c r="J21" s="202"/>
+      <c r="K21" s="202"/>
+      <c r="L21" s="202"/>
+      <c r="M21" s="202"/>
+      <c r="N21" s="202"/>
+      <c r="O21" s="203"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="238" t="s">
+      <c r="A22" s="214" t="s">
         <v>458</v>
       </c>
-      <c r="B22" s="239"/>
-      <c r="C22" s="249" t="str">
+      <c r="B22" s="215"/>
+      <c r="C22" s="216" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,16,)</f>
         <v>جدول عام</v>
       </c>
-      <c r="D22" s="240"/>
-      <c r="E22" s="240"/>
-      <c r="F22" s="240"/>
-      <c r="G22" s="240"/>
-      <c r="H22" s="240"/>
-      <c r="I22" s="240"/>
-      <c r="J22" s="240"/>
-      <c r="K22" s="240"/>
-      <c r="L22" s="240"/>
-      <c r="M22" s="240"/>
-      <c r="N22" s="240"/>
-      <c r="O22" s="241"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="202"/>
+      <c r="I22" s="202"/>
+      <c r="J22" s="202"/>
+      <c r="K22" s="202"/>
+      <c r="L22" s="202"/>
+      <c r="M22" s="202"/>
+      <c r="N22" s="202"/>
+      <c r="O22" s="203"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="231" t="s">
+      <c r="A23" s="217" t="s">
         <v>265</v>
       </c>
-      <c r="B23" s="232"/>
-      <c r="C23" s="250" t="str">
+      <c r="B23" s="218"/>
+      <c r="C23" s="219" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,11,)</f>
         <v>2021</v>
       </c>
-      <c r="D23" s="251"/>
-      <c r="E23" s="251"/>
-      <c r="F23" s="251"/>
-      <c r="G23" s="251"/>
-      <c r="H23" s="251"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="251"/>
-      <c r="K23" s="251"/>
-      <c r="L23" s="251"/>
-      <c r="M23" s="251"/>
-      <c r="N23" s="251"/>
-      <c r="O23" s="252"/>
+      <c r="D23" s="220"/>
+      <c r="E23" s="220"/>
+      <c r="F23" s="220"/>
+      <c r="G23" s="220"/>
+      <c r="H23" s="220"/>
+      <c r="I23" s="220"/>
+      <c r="J23" s="220"/>
+      <c r="K23" s="220"/>
+      <c r="L23" s="220"/>
+      <c r="M23" s="220"/>
+      <c r="N23" s="220"/>
+      <c r="O23" s="221"/>
     </row>
     <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="33"/>
@@ -17443,10 +17446,10 @@
       <c r="O24" s="36"/>
     </row>
     <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="242" t="s">
+      <c r="A25" s="208" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="243"/>
+      <c r="B25" s="209"/>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
       <c r="E25" s="35"/>
@@ -17462,70 +17465,70 @@
       <c r="O25" s="36"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="215" t="s">
+      <c r="A26" s="222" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="216"/>
-      <c r="C26" s="253">
+      <c r="B26" s="223"/>
+      <c r="C26" s="224">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,18,)</f>
         <v>45397</v>
       </c>
-      <c r="D26" s="247"/>
-      <c r="E26" s="247"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="247"/>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="247"/>
-      <c r="M26" s="247"/>
-      <c r="N26" s="247"/>
-      <c r="O26" s="248"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="225"/>
+      <c r="M26" s="225"/>
+      <c r="N26" s="225"/>
+      <c r="O26" s="226"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="220" t="s">
+      <c r="A27" s="229" t="s">
         <v>459</v>
       </c>
-      <c r="B27" s="221"/>
-      <c r="C27" s="258" t="str">
+      <c r="B27" s="230"/>
+      <c r="C27" s="231" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,19,)</f>
         <v>Villa 26 Telal Al Guziera</v>
       </c>
-      <c r="D27" s="226"/>
-      <c r="E27" s="226"/>
-      <c r="F27" s="226"/>
-      <c r="G27" s="226"/>
-      <c r="H27" s="226"/>
-      <c r="I27" s="226"/>
-      <c r="J27" s="226"/>
-      <c r="K27" s="226"/>
-      <c r="L27" s="226"/>
-      <c r="M27" s="226"/>
-      <c r="N27" s="226"/>
-      <c r="O27" s="227"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="232"/>
+      <c r="I27" s="232"/>
+      <c r="J27" s="232"/>
+      <c r="K27" s="232"/>
+      <c r="L27" s="232"/>
+      <c r="M27" s="232"/>
+      <c r="N27" s="232"/>
+      <c r="O27" s="233"/>
     </row>
     <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="231" t="s">
+      <c r="A28" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="232"/>
-      <c r="C28" s="259" t="str">
+      <c r="B28" s="218"/>
+      <c r="C28" s="234" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,20,)</f>
         <v>Sheikh Zayed</v>
       </c>
-      <c r="D28" s="251"/>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
-      <c r="I28" s="251"/>
-      <c r="J28" s="251"/>
-      <c r="K28" s="251"/>
-      <c r="L28" s="251"/>
-      <c r="M28" s="251"/>
-      <c r="N28" s="251"/>
-      <c r="O28" s="252"/>
+      <c r="D28" s="220"/>
+      <c r="E28" s="220"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="220"/>
+      <c r="H28" s="220"/>
+      <c r="I28" s="220"/>
+      <c r="J28" s="220"/>
+      <c r="K28" s="220"/>
+      <c r="L28" s="220"/>
+      <c r="M28" s="220"/>
+      <c r="N28" s="220"/>
+      <c r="O28" s="221"/>
     </row>
     <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="33"/>
@@ -17545,10 +17548,10 @@
       <c r="O29" s="36"/>
     </row>
     <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="242" t="s">
+      <c r="A30" s="208" t="s">
         <v>464</v>
       </c>
-      <c r="B30" s="243"/>
+      <c r="B30" s="209"/>
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
@@ -17564,48 +17567,48 @@
       <c r="O30" s="36"/>
     </row>
     <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="260" t="s">
+      <c r="A31" s="210" t="s">
         <v>465</v>
       </c>
-      <c r="B31" s="261"/>
-      <c r="C31" s="262" t="str">
+      <c r="B31" s="211"/>
+      <c r="C31" s="212" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,23,)</f>
         <v>010-00969141</v>
       </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="262"/>
-      <c r="G31" s="262"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="262"/>
-      <c r="J31" s="262"/>
-      <c r="K31" s="262"/>
-      <c r="L31" s="262"/>
-      <c r="M31" s="262"/>
-      <c r="N31" s="262"/>
-      <c r="O31" s="263"/>
+      <c r="D31" s="212"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="212"/>
+      <c r="I31" s="212"/>
+      <c r="J31" s="212"/>
+      <c r="K31" s="212"/>
+      <c r="L31" s="212"/>
+      <c r="M31" s="212"/>
+      <c r="N31" s="212"/>
+      <c r="O31" s="213"/>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="254" t="s">
+      <c r="A32" s="204" t="s">
         <v>466</v>
       </c>
-      <c r="B32" s="255"/>
-      <c r="C32" s="256" t="str">
+      <c r="B32" s="205"/>
+      <c r="C32" s="227" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,24,)</f>
         <v>Service Agreement</v>
       </c>
-      <c r="D32" s="256"/>
-      <c r="E32" s="256"/>
-      <c r="F32" s="256"/>
-      <c r="G32" s="256"/>
-      <c r="H32" s="256"/>
-      <c r="I32" s="256"/>
-      <c r="J32" s="256"/>
-      <c r="K32" s="256"/>
-      <c r="L32" s="256"/>
-      <c r="M32" s="256"/>
-      <c r="N32" s="256"/>
-      <c r="O32" s="257"/>
+      <c r="D32" s="227"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="227"/>
+      <c r="G32" s="227"/>
+      <c r="H32" s="227"/>
+      <c r="I32" s="227"/>
+      <c r="J32" s="227"/>
+      <c r="K32" s="227"/>
+      <c r="L32" s="227"/>
+      <c r="M32" s="227"/>
+      <c r="N32" s="227"/>
+      <c r="O32" s="228"/>
     </row>
     <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33"/>
@@ -17625,10 +17628,10 @@
       <c r="O33" s="44"/>
     </row>
     <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="242" t="s">
+      <c r="A34" s="208" t="s">
         <v>460</v>
       </c>
-      <c r="B34" s="243"/>
+      <c r="B34" s="209"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
@@ -17644,102 +17647,94 @@
       <c r="O34" s="36"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="260"/>
-      <c r="B35" s="261"/>
-      <c r="C35" s="262"/>
-      <c r="D35" s="262"/>
-      <c r="E35" s="262"/>
-      <c r="F35" s="262"/>
-      <c r="G35" s="262"/>
-      <c r="H35" s="262"/>
-      <c r="I35" s="262"/>
-      <c r="J35" s="262"/>
-      <c r="K35" s="262"/>
-      <c r="L35" s="262"/>
-      <c r="M35" s="262"/>
-      <c r="N35" s="262"/>
-      <c r="O35" s="263"/>
+      <c r="A35" s="210"/>
+      <c r="B35" s="211"/>
+      <c r="C35" s="212"/>
+      <c r="D35" s="212"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="212"/>
+      <c r="G35" s="212"/>
+      <c r="H35" s="212"/>
+      <c r="I35" s="212"/>
+      <c r="J35" s="212"/>
+      <c r="K35" s="212"/>
+      <c r="L35" s="212"/>
+      <c r="M35" s="212"/>
+      <c r="N35" s="212"/>
+      <c r="O35" s="213"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="264"/>
-      <c r="B36" s="265"/>
-      <c r="C36" s="240"/>
-      <c r="D36" s="240"/>
-      <c r="E36" s="240"/>
-      <c r="F36" s="240"/>
-      <c r="G36" s="240"/>
-      <c r="H36" s="240"/>
-      <c r="I36" s="240"/>
-      <c r="J36" s="240"/>
-      <c r="K36" s="240"/>
-      <c r="L36" s="240"/>
-      <c r="M36" s="240"/>
-      <c r="N36" s="240"/>
-      <c r="O36" s="241"/>
+      <c r="A36" s="200"/>
+      <c r="B36" s="201"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="202"/>
+      <c r="J36" s="202"/>
+      <c r="K36" s="202"/>
+      <c r="L36" s="202"/>
+      <c r="M36" s="202"/>
+      <c r="N36" s="202"/>
+      <c r="O36" s="203"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="264"/>
-      <c r="B37" s="265"/>
-      <c r="C37" s="240"/>
-      <c r="D37" s="240"/>
-      <c r="E37" s="240"/>
-      <c r="F37" s="240"/>
-      <c r="G37" s="240"/>
-      <c r="H37" s="240"/>
-      <c r="I37" s="240"/>
-      <c r="J37" s="240"/>
-      <c r="K37" s="240"/>
-      <c r="L37" s="240"/>
-      <c r="M37" s="240"/>
-      <c r="N37" s="240"/>
-      <c r="O37" s="241"/>
+      <c r="A37" s="200"/>
+      <c r="B37" s="201"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="202"/>
+      <c r="I37" s="202"/>
+      <c r="J37" s="202"/>
+      <c r="K37" s="202"/>
+      <c r="L37" s="202"/>
+      <c r="M37" s="202"/>
+      <c r="N37" s="202"/>
+      <c r="O37" s="203"/>
     </row>
     <row r="38" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="254"/>
-      <c r="B38" s="255"/>
-      <c r="C38" s="233"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="233"/>
-      <c r="H38" s="233"/>
-      <c r="I38" s="233"/>
-      <c r="J38" s="233"/>
-      <c r="K38" s="233"/>
-      <c r="L38" s="233"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="233"/>
-      <c r="O38" s="234"/>
+      <c r="A38" s="204"/>
+      <c r="B38" s="205"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="206"/>
+      <c r="I38" s="206"/>
+      <c r="J38" s="206"/>
+      <c r="K38" s="206"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="206"/>
+      <c r="O38" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:O37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:O38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:O35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:O36"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:O23"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:O32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:O28"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:O31"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:O7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:O10"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:O19"/>
     <mergeCell ref="A20:B20"/>
@@ -17755,25 +17750,33 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:O16"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:O7"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:O32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:O27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:O28"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:O31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:O23"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:O37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:O38"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:O35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:O36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/Sheets/SEPEmployees.xlsx
+++ b/Sheets/SEPEmployees.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D70378-8EF3-46A0-8C2D-0A11C39DC2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F02A791-BB29-44C2-867B-5B92D0FC4397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllOffice" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="624">
   <si>
     <t xml:space="preserve">Khaled Mohamed Helmy Mohamed Yousry Abd Rabo </t>
   </si>
@@ -1572,9 +1572,6 @@
   </si>
   <si>
     <t>Modifing Salary in Social Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahmoud Ali Mohmoud Hussein El Sayed </t>
   </si>
   <si>
     <t>Laptop / 
@@ -2038,6 +2035,12 @@
   </si>
   <si>
     <t>NationalID</t>
+  </si>
+  <si>
+    <t>EmployeeID/Code</t>
+  </si>
+  <si>
+    <t>Mahmoud Ali Mohmoud Hussein El Sayed</t>
   </si>
 </sst>
 </file>
@@ -4352,13 +4355,13 @@
         <v>67</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C1" s="72" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="72" t="s">
         <v>553</v>
-      </c>
-      <c r="D1" s="72" t="s">
-        <v>554</v>
       </c>
       <c r="E1" s="72" t="s">
         <v>64</v>
@@ -4379,7 +4382,7 @@
         <v>265</v>
       </c>
       <c r="M1" s="171" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="N1" s="173"/>
       <c r="O1" s="174" t="s">
@@ -4494,13 +4497,13 @@
         <v>277</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C3" s="159" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="165" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E3" s="102" t="s">
         <v>38</v>
@@ -4557,7 +4560,7 @@
         <v>400</v>
       </c>
       <c r="W3" s="97" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="X3" s="98" t="s">
         <v>69</v>
@@ -4567,11 +4570,11 @@
       </c>
       <c r="Z3" s="100">
         <f t="shared" ref="Z3:Z46" ca="1" si="0">DATEDIF(R3,TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA3" s="100">
         <f t="shared" ref="AA3:AA46" ca="1" si="1">DATEDIF(R3,TODAY(),"Ym")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="97" t="s">
         <v>367</v>
@@ -4588,13 +4591,13 @@
         <v>278</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C4" s="159" t="s">
         <v>167</v>
       </c>
       <c r="D4" s="165" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E4" s="102" t="s">
         <v>39</v>
@@ -4665,7 +4668,7 @@
       </c>
       <c r="AA4" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4" s="97" t="s">
         <v>364</v>
@@ -4682,16 +4685,16 @@
         <v>282</v>
       </c>
       <c r="B5" s="101" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C5" s="159" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="165" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E5" s="102" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F5" s="102" t="s">
         <v>271</v>
@@ -4759,7 +4762,7 @@
       </c>
       <c r="AA5" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="97">
         <v>12</v>
@@ -4782,7 +4785,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="166" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E6" s="102" t="s">
         <v>58</v>
@@ -4876,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="166" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E7" s="102" t="s">
         <v>59</v>
@@ -4947,7 +4950,7 @@
       </c>
       <c r="AA7" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB7" s="97">
         <v>0</v>
@@ -4970,7 +4973,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="166" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E8" s="102" t="s">
         <v>57</v>
@@ -5064,7 +5067,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="166" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E9" s="102" t="s">
         <v>57</v>
@@ -5135,7 +5138,7 @@
       </c>
       <c r="AA9" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB9" s="97">
         <v>22</v>
@@ -5158,7 +5161,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="166" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E10" s="102" t="s">
         <v>58</v>
@@ -5252,7 +5255,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="166" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E11" s="102" t="s">
         <v>60</v>
@@ -5323,7 +5326,7 @@
       </c>
       <c r="AA11" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB11" s="97">
         <v>2</v>
@@ -5346,7 +5349,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="166" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E12" s="102" t="s">
         <v>60</v>
@@ -5370,7 +5373,7 @@
         <v>343</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M12" s="104">
         <v>27902040103975</v>
@@ -5414,11 +5417,11 @@
       </c>
       <c r="Z12" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA12" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="97">
         <v>0</v>
@@ -5441,7 +5444,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="166" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E13" s="102" t="s">
         <v>57</v>
@@ -5535,7 +5538,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="141" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E14" s="128" t="s">
         <v>61</v>
@@ -5629,10 +5632,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="141" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F15" s="128" t="s">
         <v>81</v>
@@ -5698,7 +5701,7 @@
       </c>
       <c r="AA15" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB15" s="127" t="s">
         <v>366</v>
@@ -5721,7 +5724,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="141" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E16" s="128" t="s">
         <v>60</v>
@@ -5786,11 +5789,11 @@
       <c r="Y16" s="140"/>
       <c r="Z16" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="127" t="s">
         <v>366</v>
@@ -5813,7 +5816,7 @@
         <v>29</v>
       </c>
       <c r="D17" s="141" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E17" s="152" t="s">
         <v>62</v>
@@ -5907,7 +5910,7 @@
         <v>30</v>
       </c>
       <c r="D18" s="166" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E18" s="102" t="s">
         <v>62</v>
@@ -6001,7 +6004,7 @@
         <v>31</v>
       </c>
       <c r="D19" s="141" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E19" s="128" t="s">
         <v>63</v>
@@ -6095,7 +6098,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="166" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E20" s="102" t="s">
         <v>60</v>
@@ -6180,16 +6183,16 @@
     </row>
     <row r="21" spans="1:30" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="97" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B21" s="101" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="160" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D21" s="166" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E21" s="102" t="s">
         <v>62</v>
@@ -6210,7 +6213,7 @@
         <v>132</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>69</v>
@@ -6228,13 +6231,13 @@
         <v>128</v>
       </c>
       <c r="Q21" s="107" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="R21" s="108">
         <v>45323</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T21" s="12" t="s">
         <v>139</v>
@@ -6246,7 +6249,7 @@
         <v>435</v>
       </c>
       <c r="W21" s="97" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X21" s="98" t="s">
         <v>130</v>
@@ -6260,7 +6263,7 @@
       </c>
       <c r="AA21" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB21" s="97" t="s">
         <v>366</v>
@@ -6274,16 +6277,16 @@
     </row>
     <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="127" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B22" s="128" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E22" s="128" t="s">
         <v>62</v>
@@ -6301,10 +6304,10 @@
         <v>171</v>
       </c>
       <c r="J22" s="131" t="s">
+        <v>491</v>
+      </c>
+      <c r="K22" s="132" t="s">
         <v>492</v>
-      </c>
-      <c r="K22" s="132" t="s">
-        <v>493</v>
       </c>
       <c r="L22" s="133" t="s">
         <v>69</v>
@@ -6322,13 +6325,13 @@
         <v>128</v>
       </c>
       <c r="Q22" s="144" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R22" s="129">
         <v>45354</v>
       </c>
       <c r="S22" s="136" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T22" s="128" t="s">
         <v>139</v>
@@ -6340,7 +6343,7 @@
         <v>436</v>
       </c>
       <c r="W22" s="127" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="X22" s="139" t="s">
         <v>130</v>
@@ -6354,7 +6357,7 @@
       </c>
       <c r="AA22" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22" s="127" t="s">
         <v>366</v>
@@ -6368,16 +6371,16 @@
     </row>
     <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="127" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B23" s="128" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E23" s="128" t="s">
         <v>60</v>
@@ -6389,16 +6392,16 @@
         <v>35383</v>
       </c>
       <c r="H23" s="130" t="s">
+        <v>498</v>
+      </c>
+      <c r="I23" s="131" t="s">
+        <v>503</v>
+      </c>
+      <c r="J23" s="131" t="s">
+        <v>502</v>
+      </c>
+      <c r="K23" s="132" t="s">
         <v>499</v>
-      </c>
-      <c r="I23" s="131" t="s">
-        <v>504</v>
-      </c>
-      <c r="J23" s="131" t="s">
-        <v>503</v>
-      </c>
-      <c r="K23" s="132" t="s">
-        <v>500</v>
       </c>
       <c r="L23" s="133" t="s">
         <v>69</v>
@@ -6422,7 +6425,7 @@
         <v>45397</v>
       </c>
       <c r="S23" s="136" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T23" s="128" t="s">
         <v>134</v>
@@ -6434,7 +6437,7 @@
         <v>406</v>
       </c>
       <c r="W23" s="127" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="X23" s="139" t="s">
         <v>130</v>
@@ -6462,16 +6465,16 @@
     </row>
     <row r="24" spans="1:30" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="97" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B24" s="101" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="160" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D24" s="166" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E24" s="102" t="s">
         <v>62</v>
@@ -6492,7 +6495,7 @@
         <v>132</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>69</v>
@@ -6510,13 +6513,13 @@
         <v>128</v>
       </c>
       <c r="Q24" s="107" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R24" s="108">
         <v>45536</v>
       </c>
       <c r="S24" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T24" s="12" t="s">
         <v>134</v>
@@ -6528,7 +6531,7 @@
         <v>453</v>
       </c>
       <c r="W24" s="97" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="X24" s="98" t="s">
         <v>130</v>
@@ -6542,7 +6545,7 @@
       </c>
       <c r="AA24" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB24" s="97" t="s">
         <v>366</v>
@@ -6556,16 +6559,16 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="97" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B25" s="101" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="160" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D25" s="166" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E25" s="102" t="s">
         <v>57</v>
@@ -6580,13 +6583,13 @@
         <v>170</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J25" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="K25" s="18" t="s">
         <v>546</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>547</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>69</v>
@@ -6604,13 +6607,13 @@
         <v>124</v>
       </c>
       <c r="Q25" s="107" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R25" s="108">
         <v>45690</v>
       </c>
       <c r="S25" s="15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T25" s="12" t="s">
         <v>134</v>
@@ -6622,7 +6625,7 @@
         <v>406</v>
       </c>
       <c r="W25" s="97" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="X25" s="98" t="s">
         <v>130</v>
@@ -6636,10 +6639,10 @@
       </c>
       <c r="AA25" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB25" s="97" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AC25" s="97" t="s">
         <v>366</v>
@@ -6650,16 +6653,16 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="97" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B26" s="101" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="160" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D26" s="166" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E26" s="102" t="s">
         <v>62</v>
@@ -6704,10 +6707,10 @@
         <v>45872</v>
       </c>
       <c r="S26" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="T26" s="12" t="s">
         <v>596</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>597</v>
       </c>
       <c r="U26" s="14" t="s">
         <v>132</v>
@@ -6716,7 +6719,7 @@
         <v>429</v>
       </c>
       <c r="W26" s="97" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="X26" s="98" t="s">
         <v>130</v>
@@ -6730,7 +6733,7 @@
       </c>
       <c r="AA26" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB26" s="97" t="s">
         <v>366</v>
@@ -6753,7 +6756,7 @@
         <v>168</v>
       </c>
       <c r="D27" s="167" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E27" s="102" t="s">
         <v>40</v>
@@ -6848,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="168" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E28" s="102" t="s">
         <v>42</v>
@@ -6881,7 +6884,7 @@
         <v>47314</v>
       </c>
       <c r="O28" s="106" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P28" s="107" t="s">
         <v>129</v>
@@ -6943,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="168" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E29" s="102" t="s">
         <v>41</v>
@@ -6958,7 +6961,7 @@
         <v>211</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>163</v>
@@ -7015,7 +7018,7 @@
       </c>
       <c r="AA29" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB29" s="97">
         <v>5</v>
@@ -7038,7 +7041,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E30" s="128" t="s">
         <v>43</v>
@@ -7132,7 +7135,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="169" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E31" s="102" t="s">
         <v>44</v>
@@ -7204,7 +7207,7 @@
       </c>
       <c r="AA31" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31" s="97">
         <v>13</v>
@@ -7227,7 +7230,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="168" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E32" s="102" t="s">
         <v>43</v>
@@ -7322,7 +7325,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="128" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E33" s="128" t="s">
         <v>45</v>
@@ -7394,7 +7397,7 @@
       </c>
       <c r="AA33" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB33" s="127" t="s">
         <v>365</v>
@@ -7417,7 +7420,7 @@
         <v>33</v>
       </c>
       <c r="D34" s="168" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E34" s="102" t="s">
         <v>56</v>
@@ -7512,7 +7515,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="168" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E35" s="102" t="s">
         <v>46</v>
@@ -7607,7 +7610,7 @@
         <v>7</v>
       </c>
       <c r="D36" s="168" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E36" s="102" t="s">
         <v>47</v>
@@ -7679,7 +7682,7 @@
       </c>
       <c r="AA36" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB36" s="97">
         <v>16</v>
@@ -7702,7 +7705,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="168" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E37" s="102" t="s">
         <v>48</v>
@@ -7792,10 +7795,10 @@
         <v>37</v>
       </c>
       <c r="C38" s="164" t="s">
-        <v>468</v>
+        <v>623</v>
       </c>
       <c r="D38" s="170" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E38" s="102" t="s">
         <v>49</v>
@@ -7867,7 +7870,7 @@
       </c>
       <c r="AA38" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38" s="97">
         <v>15</v>
@@ -7890,7 +7893,7 @@
         <v>55</v>
       </c>
       <c r="D39" s="168" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E39" s="102" t="s">
         <v>50</v>
@@ -7985,7 +7988,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="168" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E40" s="102" t="s">
         <v>51</v>
@@ -8080,7 +8083,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="168" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E41" s="102" t="s">
         <v>52</v>
@@ -8175,7 +8178,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="168" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E42" s="102" t="s">
         <v>52</v>
@@ -8220,7 +8223,7 @@
         <v>43240</v>
       </c>
       <c r="S42" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T42" s="12" t="s">
         <v>235</v>
@@ -8270,10 +8273,10 @@
         <v>13</v>
       </c>
       <c r="D43" s="128" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E43" s="128" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F43" s="128" t="s">
         <v>189</v>
@@ -8341,7 +8344,7 @@
       </c>
       <c r="AA43" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB43" s="127" t="s">
         <v>366</v>
@@ -8361,10 +8364,10 @@
         <v>37</v>
       </c>
       <c r="C44" s="164" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D44" s="170" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E44" s="102" t="s">
         <v>53</v>
@@ -8376,7 +8379,7 @@
         <v>28126</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>369</v>
@@ -8459,7 +8462,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="170" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E45" s="102" t="s">
         <v>54</v>
@@ -8483,7 +8486,7 @@
         <v>238</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M45" s="109">
         <v>29209210103967</v>
@@ -8554,10 +8557,10 @@
         <v>164</v>
       </c>
       <c r="D46" s="170" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E46" s="102" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F46" s="102" t="s">
         <v>189</v>
@@ -8611,7 +8614,7 @@
         <v>69</v>
       </c>
       <c r="W46" s="97" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="X46" s="98" t="s">
         <v>258</v>
@@ -8640,16 +8643,16 @@
     </row>
     <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="127" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B47" s="128" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="145" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D47" s="145" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E47" s="128" t="s">
         <v>417</v>
@@ -8664,7 +8667,7 @@
         <v>230</v>
       </c>
       <c r="I47" s="146" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J47" s="131" t="s">
         <v>132</v>
@@ -8673,7 +8676,7 @@
         <v>209</v>
       </c>
       <c r="L47" s="133" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M47" s="134">
         <v>28609300107346</v>
@@ -8694,7 +8697,7 @@
         <v>45302</v>
       </c>
       <c r="S47" s="136" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="T47" s="128" t="s">
         <v>339</v>
@@ -8706,7 +8709,7 @@
         <v>412</v>
       </c>
       <c r="W47" s="127" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X47" s="139" t="s">
         <v>391</v>
@@ -8732,19 +8735,19 @@
     </row>
     <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="127" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B48" s="128" t="s">
         <v>37</v>
       </c>
       <c r="C48" s="145" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D48" s="145" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E48" s="128" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F48" s="128" t="s">
         <v>74</v>
@@ -8756,7 +8759,7 @@
         <v>211</v>
       </c>
       <c r="I48" s="131" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J48" s="131" t="s">
         <v>132</v>
@@ -8765,7 +8768,7 @@
         <v>248</v>
       </c>
       <c r="L48" s="133" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M48" s="134">
         <v>30011262103079</v>
@@ -8786,7 +8789,7 @@
         <v>45397</v>
       </c>
       <c r="S48" s="136" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T48" s="128" t="s">
         <v>153</v>
@@ -8798,7 +8801,7 @@
         <v>452</v>
       </c>
       <c r="W48" s="127" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="X48" s="139" t="s">
         <v>391</v>
@@ -8827,19 +8830,19 @@
     </row>
     <row r="49" spans="1:30" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="97" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B49" s="101" t="s">
         <v>37</v>
       </c>
       <c r="C49" s="164" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D49" s="170" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E49" s="102" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F49" s="102" t="s">
         <v>189</v>
@@ -8848,19 +8851,19 @@
         <v>24285</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>74</v>
       </c>
       <c r="J49" s="147" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M49" s="154">
         <v>26606272101039</v>
@@ -8881,7 +8884,7 @@
         <v>45438</v>
       </c>
       <c r="S49" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T49" s="12" t="s">
         <v>146</v>
@@ -8893,7 +8896,7 @@
         <v>412</v>
       </c>
       <c r="W49" s="97" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X49" s="98" t="s">
         <v>258</v>
@@ -8911,7 +8914,7 @@
         <v>7</v>
       </c>
       <c r="AB49" s="97" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AC49" s="97" t="s">
         <v>366</v>
@@ -8922,19 +8925,19 @@
     </row>
     <row r="50" spans="1:30" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="97" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B50" s="101" t="s">
         <v>37</v>
       </c>
       <c r="C50" s="164" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="D50" s="170" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E50" s="102" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F50" s="102" t="s">
         <v>74</v>
@@ -8949,13 +8952,13 @@
         <v>74</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K50" s="18" t="s">
         <v>248</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M50" s="109">
         <v>30008310100574</v>
@@ -8976,7 +8979,7 @@
         <v>45505</v>
       </c>
       <c r="S50" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="T50" s="12" t="s">
         <v>134</v>
@@ -8988,7 +8991,7 @@
         <v>452</v>
       </c>
       <c r="W50" s="97" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="X50" s="98" t="s">
         <v>258</v>
@@ -9003,7 +9006,7 @@
       </c>
       <c r="AA50" s="100">
         <f ca="1">DATEDIF(R50,TODAY(),"Ym")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB50" s="97" t="s">
         <v>366</v>
@@ -9017,16 +9020,16 @@
     </row>
     <row r="51" spans="1:30" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="97" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B51" s="101" t="s">
         <v>37</v>
       </c>
       <c r="C51" s="164" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D51" s="170" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E51" s="102" t="s">
         <v>45</v>
@@ -9038,16 +9041,16 @@
         <v>35128</v>
       </c>
       <c r="H51" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="I51" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="J51" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="K51" s="18" t="s">
         <v>616</v>
-      </c>
-      <c r="J51" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="K51" s="18" t="s">
-        <v>617</v>
       </c>
       <c r="L51" s="16">
         <v>69654522</v>
@@ -9071,7 +9074,7 @@
         <v>46012</v>
       </c>
       <c r="S51" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="T51" s="12" t="s">
         <v>159</v>
@@ -9083,7 +9086,7 @@
         <v>437</v>
       </c>
       <c r="W51" s="97" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="X51" s="98" t="s">
         <v>258</v>
@@ -10536,7 +10539,7 @@
         <v>467</v>
       </c>
       <c r="D114" s="47" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -11125,7 +11128,7 @@
         <v>45975</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D165" s="49"/>
     </row>
@@ -11137,7 +11140,7 @@
         <v>45791</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D166" s="49"/>
     </row>
@@ -11149,7 +11152,7 @@
         <v>45610</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D167" s="49"/>
     </row>
@@ -11957,10 +11960,10 @@
     </row>
     <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="62" t="s">
+        <v>471</v>
+      </c>
+      <c r="B238" s="185" t="s">
         <v>472</v>
-      </c>
-      <c r="B238" s="185" t="s">
-        <v>473</v>
       </c>
       <c r="C238" s="186"/>
       <c r="D238" s="53">
@@ -11991,10 +11994,10 @@
     </row>
     <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="62" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B241" s="185" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C241" s="186"/>
       <c r="D241" s="53">
@@ -12025,10 +12028,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="62" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B244" s="185" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C244" s="186"/>
       <c r="D244" s="53">
@@ -12081,10 +12084,10 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="62" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B249" s="185" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C249" s="186"/>
       <c r="D249" s="53">
@@ -12137,10 +12140,10 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="62" t="s">
+        <v>610</v>
+      </c>
+      <c r="B254" s="185" t="s">
         <v>611</v>
-      </c>
-      <c r="B254" s="185" t="s">
-        <v>612</v>
       </c>
       <c r="C254" s="186"/>
       <c r="D254" s="53">
@@ -12333,27 +12336,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" style="125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="125" customWidth="1"/>
+    <col min="2" max="2" width="56" style="19" customWidth="1"/>
     <col min="3" max="9" width="12.33203125" style="19" customWidth="1"/>
     <col min="10" max="11" width="11.77734375" style="19" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" style="19" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" style="19" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" style="19" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" style="52" customWidth="1"/>
     <col min="16" max="16" width="10.77734375" style="19" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="115" t="s">
-        <v>67</v>
+        <v>622</v>
       </c>
       <c r="B1" s="115" t="s">
         <v>34</v>
@@ -12389,7 +12392,7 @@
         <v>318</v>
       </c>
       <c r="M1" s="115" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N1" s="115" t="s">
         <v>327</v>
@@ -12951,7 +12954,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
         <v>288</v>
       </c>
@@ -13001,7 +13004,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="64" t="s">
         <v>289</v>
       </c>
@@ -13051,7 +13054,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="64" t="s">
         <v>290</v>
       </c>
@@ -13101,7 +13104,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="150" t="s">
         <v>291</v>
       </c>
@@ -13201,7 +13204,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="150" t="s">
         <v>293</v>
       </c>
@@ -13303,10 +13306,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="124" t="s">
+        <v>478</v>
+      </c>
+      <c r="B20" s="112" t="s">
         <v>479</v>
-      </c>
-      <c r="B20" s="112" t="s">
-        <v>480</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>320</v>
@@ -13353,10 +13356,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="124" t="s">
+        <v>489</v>
+      </c>
+      <c r="B21" s="112" t="s">
         <v>490</v>
-      </c>
-      <c r="B21" s="112" t="s">
-        <v>491</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>320</v>
@@ -13401,12 +13404,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="150" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="153" t="s">
         <v>497</v>
-      </c>
-      <c r="B22" s="153" t="s">
-        <v>498</v>
       </c>
       <c r="C22" s="64" t="s">
         <v>321</v>
@@ -13453,10 +13456,10 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="124" t="s">
+        <v>533</v>
+      </c>
+      <c r="B23" s="126" t="s">
         <v>534</v>
-      </c>
-      <c r="B23" s="126" t="s">
-        <v>535</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>320</v>
@@ -13503,10 +13506,10 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="124" t="s">
+        <v>543</v>
+      </c>
+      <c r="B24" s="126" t="s">
         <v>544</v>
-      </c>
-      <c r="B24" s="126" t="s">
-        <v>545</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>320</v>
@@ -13553,10 +13556,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="124" t="s">
+        <v>592</v>
+      </c>
+      <c r="B25" s="126" t="s">
         <v>593</v>
-      </c>
-      <c r="B25" s="126" t="s">
-        <v>594</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>320</v>
@@ -13751,7 +13754,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="64" t="s">
         <v>298</v>
       </c>
@@ -13889,7 +13892,7 @@
         <v>320</v>
       </c>
       <c r="M31" s="112" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N31" s="25" t="s">
         <v>320</v>
@@ -14156,7 +14159,7 @@
         <v>306</v>
       </c>
       <c r="B37" s="112" t="s">
-        <v>9</v>
+        <v>623</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>320</v>
@@ -14401,7 +14404,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="150" t="s">
         <v>312</v>
       </c>
@@ -14601,12 +14604,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="150" t="s">
+        <v>471</v>
+      </c>
+      <c r="B46" s="64" t="s">
         <v>472</v>
-      </c>
-      <c r="B46" s="64" t="s">
-        <v>473</v>
       </c>
       <c r="C46" s="64" t="s">
         <v>320</v>
@@ -14651,12 +14654,12 @@
         <v>385</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="150" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C47" s="64" t="s">
         <v>320</v>
@@ -14703,10 +14706,10 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="124" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B48" s="112" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C48" s="25" t="s">
         <v>320</v>
@@ -14753,10 +14756,10 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="124" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B49" s="112" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C49" s="25" t="s">
         <v>320</v>
@@ -14803,10 +14806,10 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="124" t="s">
+        <v>610</v>
+      </c>
+      <c r="B50" s="112" t="s">
         <v>611</v>
-      </c>
-      <c r="B50" s="112" t="s">
-        <v>612</v>
       </c>
       <c r="C50" s="25" t="s">
         <v>320</v>
@@ -14852,13 +14855,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P50" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="15">
-      <filters>
-        <filter val="Active"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P50" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -16646,13 +16643,13 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>417</v>
@@ -16675,16 +16672,16 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>74</v>
@@ -16704,13 +16701,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>60</v>
@@ -16969,7 +16966,7 @@
         <v>374</v>
       </c>
       <c r="B2" s="254" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C2" s="254"/>
       <c r="D2" s="254"/>

--- a/Sheets/SEPEmployees.xlsx
+++ b/Sheets/SEPEmployees.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F02A791-BB29-44C2-867B-5B92D0FC4397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDB869F-EA4C-4299-992E-721BF078D080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllOffice" sheetId="1" r:id="rId1"/>
@@ -3562,18 +3562,27 @@
     <xf numFmtId="0" fontId="5" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3601,215 +3610,206 @@
     <xf numFmtId="15" fontId="25" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="16" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="16" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4316,7 +4316,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD54"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5527,7 +5526,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="127" t="s">
         <v>288</v>
       </c>
@@ -5621,7 +5620,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="127" t="s">
         <v>289</v>
       </c>
@@ -5713,7 +5712,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="127" t="s">
         <v>290</v>
       </c>
@@ -5805,7 +5804,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="127" t="s">
         <v>291</v>
       </c>
@@ -5993,7 +5992,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="127" t="s">
         <v>293</v>
       </c>
@@ -6275,7 +6274,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="127" t="s">
         <v>489</v>
       </c>
@@ -6369,7 +6368,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="127" t="s">
         <v>496</v>
       </c>
@@ -7030,7 +7029,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="127" t="s">
         <v>298</v>
       </c>
@@ -7314,7 +7313,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="33" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="127" t="s">
         <v>301</v>
       </c>
@@ -8262,7 +8261,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="127" t="s">
         <v>311</v>
       </c>
@@ -8534,7 +8533,7 @@
       </c>
       <c r="AA45" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB45" s="97" t="s">
         <v>366</v>
@@ -8641,7 +8640,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="127" t="s">
         <v>471</v>
       </c>
@@ -8733,7 +8732,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" s="127" t="s">
         <v>504</v>
       </c>
@@ -9210,11 +9209,6 @@
     <filterColumn colId="23" showButton="0"/>
     <filterColumn colId="25" showButton="0"/>
     <filterColumn colId="27" showButton="0"/>
-    <filterColumn colId="29">
-      <filters blank="1">
-        <filter val="Active"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="S1:U1"/>
@@ -9249,14 +9243,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="183" t="s">
+      <c r="A1" s="188" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="184" t="s">
+      <c r="B1" s="188"/>
+      <c r="C1" s="189" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="183" t="s">
+      <c r="D1" s="188" t="s">
         <v>260</v>
       </c>
     </row>
@@ -9267,17 +9261,17 @@
       <c r="B2" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="183"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="188"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="190" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="188"/>
+      <c r="C3" s="191"/>
       <c r="D3" s="53">
         <v>46219</v>
       </c>
@@ -9448,10 +9442,10 @@
       <c r="A18" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="185" t="s">
+      <c r="B18" s="183" t="s">
         <v>379</v>
       </c>
-      <c r="C18" s="186"/>
+      <c r="C18" s="184"/>
       <c r="D18" s="53">
         <v>46042</v>
       </c>
@@ -9622,10 +9616,10 @@
       <c r="A33" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="B33" s="185" t="s">
+      <c r="B33" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="186"/>
+      <c r="C33" s="184"/>
       <c r="D33" s="53">
         <v>46126</v>
       </c>
@@ -9754,21 +9748,21 @@
       <c r="A45" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="B45" s="189" t="s">
+      <c r="B45" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="190"/>
+      <c r="C45" s="193"/>
       <c r="D45" s="66">
         <v>45274</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="193" t="s">
+      <c r="A46" s="196" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="194"/>
-      <c r="C46" s="194"/>
-      <c r="D46" s="195"/>
+      <c r="B46" s="197"/>
+      <c r="C46" s="197"/>
+      <c r="D46" s="198"/>
     </row>
     <row r="47" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="67">
@@ -9836,10 +9830,10 @@
       <c r="A52" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="B52" s="185" t="s">
+      <c r="B52" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="186"/>
+      <c r="C52" s="184"/>
       <c r="D52" s="53">
         <v>46162</v>
       </c>
@@ -9970,10 +9964,10 @@
       <c r="A64" s="51" t="s">
         <v>300</v>
       </c>
-      <c r="B64" s="185" t="s">
+      <c r="B64" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C64" s="186"/>
+      <c r="C64" s="184"/>
       <c r="D64" s="53">
         <v>46090</v>
       </c>
@@ -10084,10 +10078,10 @@
       <c r="A74" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="185" t="s">
+      <c r="B74" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="186"/>
+      <c r="C74" s="184"/>
       <c r="D74" s="53">
         <v>46053</v>
       </c>
@@ -10170,10 +10164,10 @@
       <c r="A82" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="191" t="s">
+      <c r="B82" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="C82" s="192"/>
+      <c r="C82" s="195"/>
       <c r="D82" s="53">
         <v>46314</v>
       </c>
@@ -10332,10 +10326,10 @@
       <c r="A96" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="B96" s="185" t="s">
+      <c r="B96" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C96" s="186"/>
+      <c r="C96" s="184"/>
       <c r="D96" s="53">
         <v>46049</v>
       </c>
@@ -10478,10 +10472,10 @@
       <c r="A109" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="185" t="s">
+      <c r="B109" s="183" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="186"/>
+      <c r="C109" s="184"/>
       <c r="D109" s="53">
         <v>46190</v>
       </c>
@@ -10560,10 +10554,10 @@
       <c r="A116" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="B116" s="185" t="s">
+      <c r="B116" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="C116" s="186"/>
+      <c r="C116" s="184"/>
       <c r="D116" s="53">
         <v>46022</v>
       </c>
@@ -10746,10 +10740,10 @@
       <c r="A132" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="B132" s="185" t="s">
+      <c r="B132" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="186"/>
+      <c r="C132" s="184"/>
       <c r="D132" s="53">
         <v>46203</v>
       </c>
@@ -10908,10 +10902,10 @@
       <c r="A146" s="51" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="185" t="s">
+      <c r="B146" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="C146" s="186"/>
+      <c r="C146" s="184"/>
       <c r="D146" s="53">
         <v>46217</v>
       </c>
@@ -11094,10 +11088,10 @@
       <c r="A162" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="B162" s="185" t="s">
+      <c r="B162" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="186"/>
+      <c r="C162" s="184"/>
       <c r="D162" s="53">
         <v>46340</v>
       </c>
@@ -11328,10 +11322,10 @@
       <c r="A182" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="B182" s="185" t="s">
+      <c r="B182" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="C182" s="186"/>
+      <c r="C182" s="184"/>
       <c r="D182" s="53">
         <v>46202</v>
       </c>
@@ -11514,10 +11508,10 @@
       <c r="A198" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="B198" s="185" t="s">
+      <c r="B198" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="C198" s="186"/>
+      <c r="C198" s="184"/>
       <c r="D198" s="53">
         <v>46345</v>
       </c>
@@ -11654,10 +11648,10 @@
       <c r="A210" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="B210" s="185" t="s">
+      <c r="B210" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="186"/>
+      <c r="C210" s="184"/>
       <c r="D210" s="53">
         <v>46222</v>
       </c>
@@ -11756,10 +11750,10 @@
       <c r="A219" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="B219" s="185" t="s">
+      <c r="B219" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C219" s="186"/>
+      <c r="C219" s="184"/>
       <c r="D219" s="53">
         <v>46084</v>
       </c>
@@ -11812,10 +11806,10 @@
       <c r="A224" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="B224" s="185" t="s">
+      <c r="B224" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C224" s="186"/>
+      <c r="C224" s="184"/>
       <c r="D224" s="53">
         <v>46006</v>
       </c>
@@ -11869,13 +11863,13 @@
       <c r="D229" s="48"/>
     </row>
     <row r="230" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="51" t="s">
-        <v>289</v>
-      </c>
-      <c r="B230" s="185" t="s">
+      <c r="A230" s="62" t="s">
+        <v>286</v>
+      </c>
+      <c r="B230" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="C230" s="186"/>
+      <c r="C230" s="184"/>
       <c r="D230" s="53">
         <v>46203</v>
       </c>
@@ -11962,21 +11956,21 @@
       <c r="A238" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="B238" s="185" t="s">
+      <c r="B238" s="183" t="s">
         <v>472</v>
       </c>
-      <c r="C238" s="186"/>
+      <c r="C238" s="184"/>
       <c r="D238" s="53">
         <v>45460</v>
       </c>
     </row>
     <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="196" t="s">
+      <c r="A239" s="185" t="s">
         <v>385</v>
       </c>
-      <c r="B239" s="197"/>
-      <c r="C239" s="197"/>
-      <c r="D239" s="198"/>
+      <c r="B239" s="186"/>
+      <c r="C239" s="186"/>
+      <c r="D239" s="187"/>
     </row>
     <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="48">
@@ -11996,21 +11990,21 @@
       <c r="A241" s="62" t="s">
         <v>504</v>
       </c>
-      <c r="B241" s="185" t="s">
+      <c r="B241" s="183" t="s">
         <v>509</v>
       </c>
-      <c r="C241" s="186"/>
+      <c r="C241" s="184"/>
       <c r="D241" s="53">
         <v>45579</v>
       </c>
     </row>
     <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="196" t="s">
+      <c r="A242" s="185" t="s">
         <v>385</v>
       </c>
-      <c r="B242" s="197"/>
-      <c r="C242" s="197"/>
-      <c r="D242" s="198"/>
+      <c r="B242" s="186"/>
+      <c r="C242" s="186"/>
+      <c r="D242" s="187"/>
     </row>
     <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="48">
@@ -12030,10 +12024,10 @@
       <c r="A244" s="62" t="s">
         <v>513</v>
       </c>
-      <c r="B244" s="185" t="s">
+      <c r="B244" s="183" t="s">
         <v>523</v>
       </c>
-      <c r="C244" s="186"/>
+      <c r="C244" s="184"/>
       <c r="D244" s="53">
         <v>46167</v>
       </c>
@@ -12086,10 +12080,10 @@
       <c r="A249" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="B249" s="185" t="s">
+      <c r="B249" s="183" t="s">
         <v>528</v>
       </c>
-      <c r="C249" s="186"/>
+      <c r="C249" s="184"/>
       <c r="D249" s="53">
         <v>46234</v>
       </c>
@@ -12142,10 +12136,10 @@
       <c r="A254" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="B254" s="185" t="s">
+      <c r="B254" s="183" t="s">
         <v>611</v>
       </c>
-      <c r="C254" s="186"/>
+      <c r="C254" s="184"/>
       <c r="D254" s="53">
         <v>46194</v>
       </c>
@@ -12172,6 +12166,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B109:C109"/>
     <mergeCell ref="B254:C254"/>
     <mergeCell ref="B146:C146"/>
     <mergeCell ref="B162:C162"/>
@@ -12188,21 +12197,6 @@
     <mergeCell ref="A239:D239"/>
     <mergeCell ref="A242:D242"/>
     <mergeCell ref="B249:C249"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B109:C109"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="timePeriod" dxfId="24" priority="34" timePeriod="nextWeek">
@@ -16943,49 +16937,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="200" t="s">
         <v>373</v>
       </c>
-      <c r="B1" s="252"/>
-      <c r="C1" s="252"/>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="252"/>
-      <c r="H1" s="252"/>
-      <c r="I1" s="252"/>
-      <c r="J1" s="252"/>
-      <c r="K1" s="252"/>
-      <c r="L1" s="252"/>
-      <c r="M1" s="252"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="253"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="201"/>
+      <c r="M1" s="201"/>
+      <c r="N1" s="201"/>
+      <c r="O1" s="202"/>
     </row>
     <row r="2" spans="1:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="203" t="s">
         <v>496</v>
       </c>
-      <c r="C2" s="254"/>
-      <c r="D2" s="254"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="256" t="s">
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="205" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="259" t="str">
+      <c r="G2" s="206"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,2,)</f>
         <v>Lawyer</v>
       </c>
-      <c r="J2" s="260"/>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="261"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
+      <c r="M2" s="209"/>
+      <c r="N2" s="209"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37"/>
@@ -17005,18 +16999,18 @@
       <c r="O3" s="42"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="262" t="s">
+      <c r="A4" s="211" t="s">
         <v>461</v>
       </c>
-      <c r="B4" s="263"/>
+      <c r="B4" s="212"/>
       <c r="C4" s="34"/>
       <c r="D4" s="43"/>
       <c r="E4" s="43"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="264"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
       <c r="M4" s="35"/>
@@ -17024,136 +17018,136 @@
       <c r="O4" s="44"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="222" t="s">
+      <c r="A5" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="223"/>
-      <c r="C5" s="245" t="str">
+      <c r="B5" s="216"/>
+      <c r="C5" s="217" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,3,)</f>
         <v>Hussien Sherif Mohamed Monier Amer</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="246"/>
-      <c r="O5" s="247"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+      <c r="N5" s="218"/>
+      <c r="O5" s="219"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="220" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="248" t="str">
+      <c r="B6" s="221"/>
+      <c r="C6" s="222" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,17,)</f>
         <v>-</v>
       </c>
-      <c r="D6" s="249"/>
-      <c r="E6" s="249"/>
-      <c r="F6" s="249"/>
-      <c r="G6" s="249"/>
-      <c r="H6" s="249"/>
-      <c r="I6" s="249"/>
-      <c r="J6" s="249"/>
-      <c r="K6" s="249"/>
-      <c r="L6" s="249"/>
-      <c r="M6" s="249"/>
-      <c r="N6" s="249"/>
-      <c r="O6" s="250"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="223"/>
+      <c r="O6" s="224"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="229" t="s">
+      <c r="A7" s="220" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="230"/>
-      <c r="C7" s="241" t="str">
+      <c r="B7" s="221"/>
+      <c r="C7" s="225" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,4,)</f>
         <v>حسين شريف محمد منير عامر</v>
       </c>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="232"/>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
-      <c r="K7" s="232"/>
-      <c r="L7" s="232"/>
-      <c r="M7" s="232"/>
-      <c r="N7" s="232"/>
-      <c r="O7" s="233"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="227"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="229" t="s">
+      <c r="A8" s="220" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="230"/>
-      <c r="C8" s="241" t="str">
+      <c r="B8" s="221"/>
+      <c r="C8" s="225" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,5,)</f>
         <v xml:space="preserve">Associate </v>
       </c>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="233"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="226"/>
+      <c r="O8" s="227"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="229" t="s">
+      <c r="A9" s="220" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="230"/>
-      <c r="C9" s="242" t="str">
+      <c r="B9" s="221"/>
+      <c r="C9" s="228" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,6,)</f>
         <v>Banking &amp; Procedures</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="E9" s="243"/>
-      <c r="F9" s="243"/>
-      <c r="G9" s="243"/>
-      <c r="H9" s="243"/>
-      <c r="I9" s="243"/>
-      <c r="J9" s="243"/>
-      <c r="K9" s="243"/>
-      <c r="L9" s="243"/>
-      <c r="M9" s="243"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="244"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="230"/>
     </row>
     <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="217" t="s">
+      <c r="A10" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="218"/>
-      <c r="C10" s="206">
+      <c r="B10" s="232"/>
+      <c r="C10" s="233">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,22,)</f>
         <v>406</v>
       </c>
-      <c r="D10" s="206"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="206"/>
-      <c r="G10" s="206"/>
-      <c r="H10" s="206"/>
-      <c r="I10" s="206"/>
-      <c r="J10" s="206"/>
-      <c r="K10" s="206"/>
-      <c r="L10" s="206"/>
-      <c r="M10" s="206"/>
-      <c r="N10" s="206"/>
-      <c r="O10" s="207"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="233"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="234"/>
     </row>
     <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33"/>
@@ -17173,111 +17167,111 @@
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="208" t="s">
+      <c r="A12" s="242" t="s">
         <v>454</v>
       </c>
-      <c r="B12" s="209"/>
-      <c r="C12" s="238"/>
-      <c r="D12" s="238"/>
-      <c r="E12" s="238"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238"/>
-      <c r="L12" s="238"/>
-      <c r="M12" s="238"/>
-      <c r="N12" s="238"/>
-      <c r="O12" s="239"/>
+      <c r="B12" s="243"/>
+      <c r="C12" s="244"/>
+      <c r="D12" s="244"/>
+      <c r="E12" s="244"/>
+      <c r="F12" s="244"/>
+      <c r="G12" s="244"/>
+      <c r="H12" s="244"/>
+      <c r="I12" s="244"/>
+      <c r="J12" s="244"/>
+      <c r="K12" s="244"/>
+      <c r="L12" s="244"/>
+      <c r="M12" s="244"/>
+      <c r="N12" s="244"/>
+      <c r="O12" s="245"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="222" t="s">
+      <c r="A13" s="215" t="s">
         <v>455</v>
       </c>
-      <c r="B13" s="223"/>
-      <c r="C13" s="240">
+      <c r="B13" s="216"/>
+      <c r="C13" s="246">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,7,)</f>
         <v>35383</v>
       </c>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="225"/>
-      <c r="H13" s="225"/>
-      <c r="I13" s="225"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="225"/>
-      <c r="M13" s="225"/>
-      <c r="N13" s="225"/>
-      <c r="O13" s="226"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="247"/>
+      <c r="K13" s="247"/>
+      <c r="L13" s="247"/>
+      <c r="M13" s="247"/>
+      <c r="N13" s="247"/>
+      <c r="O13" s="248"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="229" t="s">
+      <c r="A14" s="220" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="230"/>
-      <c r="C14" s="241" t="str">
+      <c r="B14" s="221"/>
+      <c r="C14" s="225" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,8,)</f>
         <v>Master of Laws</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="232"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="232"/>
-      <c r="I14" s="232"/>
-      <c r="J14" s="232"/>
-      <c r="K14" s="232"/>
-      <c r="L14" s="232"/>
-      <c r="M14" s="232"/>
-      <c r="N14" s="232"/>
-      <c r="O14" s="233"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="226"/>
+      <c r="H14" s="226"/>
+      <c r="I14" s="226"/>
+      <c r="J14" s="226"/>
+      <c r="K14" s="226"/>
+      <c r="L14" s="226"/>
+      <c r="M14" s="226"/>
+      <c r="N14" s="226"/>
+      <c r="O14" s="227"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="214" t="s">
+      <c r="A15" s="238" t="s">
         <v>456</v>
       </c>
-      <c r="B15" s="215"/>
-      <c r="C15" s="216" t="str">
+      <c r="B15" s="239"/>
+      <c r="C15" s="249" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,9,)</f>
         <v>Professional Legal Practice</v>
       </c>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="202"/>
-      <c r="G15" s="202"/>
-      <c r="H15" s="202"/>
-      <c r="I15" s="202"/>
-      <c r="J15" s="202"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="202"/>
-      <c r="N15" s="202"/>
-      <c r="O15" s="203"/>
+      <c r="D15" s="240"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="240"/>
+      <c r="G15" s="240"/>
+      <c r="H15" s="240"/>
+      <c r="I15" s="240"/>
+      <c r="J15" s="240"/>
+      <c r="K15" s="240"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="240"/>
+      <c r="O15" s="241"/>
     </row>
     <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="217" t="s">
+      <c r="A16" s="231" t="s">
         <v>463</v>
       </c>
-      <c r="B16" s="218"/>
-      <c r="C16" s="219" t="str">
+      <c r="B16" s="232"/>
+      <c r="C16" s="250" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,10,)</f>
         <v>University of Law</v>
       </c>
-      <c r="D16" s="220"/>
-      <c r="E16" s="220"/>
-      <c r="F16" s="220"/>
-      <c r="G16" s="220"/>
-      <c r="H16" s="220"/>
-      <c r="I16" s="220"/>
-      <c r="J16" s="220"/>
-      <c r="K16" s="220"/>
-      <c r="L16" s="220"/>
-      <c r="M16" s="220"/>
-      <c r="N16" s="220"/>
-      <c r="O16" s="221"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="251"/>
+      <c r="K16" s="251"/>
+      <c r="L16" s="251"/>
+      <c r="M16" s="251"/>
+      <c r="N16" s="251"/>
+      <c r="O16" s="252"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="33"/>
@@ -17297,10 +17291,10 @@
       <c r="O17" s="36"/>
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="208" t="s">
+      <c r="A18" s="242" t="s">
         <v>462</v>
       </c>
-      <c r="B18" s="209"/>
+      <c r="B18" s="243"/>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
@@ -17316,10 +17310,10 @@
       <c r="O18" s="36"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="222" t="s">
+      <c r="A19" s="215" t="s">
         <v>376</v>
       </c>
-      <c r="B19" s="223"/>
+      <c r="B19" s="216"/>
       <c r="C19" s="235" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,12,)</f>
         <v>-</v>
@@ -17338,92 +17332,92 @@
       <c r="O19" s="237"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="214" t="s">
+      <c r="A20" s="238" t="s">
         <v>457</v>
       </c>
-      <c r="B20" s="215"/>
-      <c r="C20" s="202">
+      <c r="B20" s="239"/>
+      <c r="C20" s="240">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,14,)</f>
         <v>47469</v>
       </c>
-      <c r="D20" s="202"/>
-      <c r="E20" s="202"/>
-      <c r="F20" s="202"/>
-      <c r="G20" s="202"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="202"/>
-      <c r="N20" s="202"/>
-      <c r="O20" s="203"/>
+      <c r="D20" s="240"/>
+      <c r="E20" s="240"/>
+      <c r="F20" s="240"/>
+      <c r="G20" s="240"/>
+      <c r="H20" s="240"/>
+      <c r="I20" s="240"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="240"/>
+      <c r="L20" s="240"/>
+      <c r="M20" s="240"/>
+      <c r="N20" s="240"/>
+      <c r="O20" s="241"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="214" t="s">
+      <c r="A21" s="238" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="215"/>
-      <c r="C21" s="216">
+      <c r="B21" s="239"/>
+      <c r="C21" s="249">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,15,)</f>
         <v>710391</v>
       </c>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="202"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="202"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="202"/>
-      <c r="N21" s="202"/>
-      <c r="O21" s="203"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="240"/>
+      <c r="F21" s="240"/>
+      <c r="G21" s="240"/>
+      <c r="H21" s="240"/>
+      <c r="I21" s="240"/>
+      <c r="J21" s="240"/>
+      <c r="K21" s="240"/>
+      <c r="L21" s="240"/>
+      <c r="M21" s="240"/>
+      <c r="N21" s="240"/>
+      <c r="O21" s="241"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="214" t="s">
+      <c r="A22" s="238" t="s">
         <v>458</v>
       </c>
-      <c r="B22" s="215"/>
-      <c r="C22" s="216" t="str">
+      <c r="B22" s="239"/>
+      <c r="C22" s="249" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,16,)</f>
         <v>جدول عام</v>
       </c>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="202"/>
-      <c r="N22" s="202"/>
-      <c r="O22" s="203"/>
+      <c r="D22" s="240"/>
+      <c r="E22" s="240"/>
+      <c r="F22" s="240"/>
+      <c r="G22" s="240"/>
+      <c r="H22" s="240"/>
+      <c r="I22" s="240"/>
+      <c r="J22" s="240"/>
+      <c r="K22" s="240"/>
+      <c r="L22" s="240"/>
+      <c r="M22" s="240"/>
+      <c r="N22" s="240"/>
+      <c r="O22" s="241"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="217" t="s">
+      <c r="A23" s="231" t="s">
         <v>265</v>
       </c>
-      <c r="B23" s="218"/>
-      <c r="C23" s="219" t="str">
+      <c r="B23" s="232"/>
+      <c r="C23" s="250" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,11,)</f>
         <v>2021</v>
       </c>
-      <c r="D23" s="220"/>
-      <c r="E23" s="220"/>
-      <c r="F23" s="220"/>
-      <c r="G23" s="220"/>
-      <c r="H23" s="220"/>
-      <c r="I23" s="220"/>
-      <c r="J23" s="220"/>
-      <c r="K23" s="220"/>
-      <c r="L23" s="220"/>
-      <c r="M23" s="220"/>
-      <c r="N23" s="220"/>
-      <c r="O23" s="221"/>
+      <c r="D23" s="251"/>
+      <c r="E23" s="251"/>
+      <c r="F23" s="251"/>
+      <c r="G23" s="251"/>
+      <c r="H23" s="251"/>
+      <c r="I23" s="251"/>
+      <c r="J23" s="251"/>
+      <c r="K23" s="251"/>
+      <c r="L23" s="251"/>
+      <c r="M23" s="251"/>
+      <c r="N23" s="251"/>
+      <c r="O23" s="252"/>
     </row>
     <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="33"/>
@@ -17443,10 +17437,10 @@
       <c r="O24" s="36"/>
     </row>
     <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="208" t="s">
+      <c r="A25" s="242" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="209"/>
+      <c r="B25" s="243"/>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
       <c r="E25" s="35"/>
@@ -17462,70 +17456,70 @@
       <c r="O25" s="36"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="222" t="s">
+      <c r="A26" s="215" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="223"/>
-      <c r="C26" s="224">
+      <c r="B26" s="216"/>
+      <c r="C26" s="253">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,18,)</f>
         <v>45397</v>
       </c>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="225"/>
-      <c r="G26" s="225"/>
-      <c r="H26" s="225"/>
-      <c r="I26" s="225"/>
-      <c r="J26" s="225"/>
-      <c r="K26" s="225"/>
-      <c r="L26" s="225"/>
-      <c r="M26" s="225"/>
-      <c r="N26" s="225"/>
-      <c r="O26" s="226"/>
+      <c r="D26" s="247"/>
+      <c r="E26" s="247"/>
+      <c r="F26" s="247"/>
+      <c r="G26" s="247"/>
+      <c r="H26" s="247"/>
+      <c r="I26" s="247"/>
+      <c r="J26" s="247"/>
+      <c r="K26" s="247"/>
+      <c r="L26" s="247"/>
+      <c r="M26" s="247"/>
+      <c r="N26" s="247"/>
+      <c r="O26" s="248"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="229" t="s">
+      <c r="A27" s="220" t="s">
         <v>459</v>
       </c>
-      <c r="B27" s="230"/>
-      <c r="C27" s="231" t="str">
+      <c r="B27" s="221"/>
+      <c r="C27" s="258" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,19,)</f>
         <v>Villa 26 Telal Al Guziera</v>
       </c>
-      <c r="D27" s="232"/>
-      <c r="E27" s="232"/>
-      <c r="F27" s="232"/>
-      <c r="G27" s="232"/>
-      <c r="H27" s="232"/>
-      <c r="I27" s="232"/>
-      <c r="J27" s="232"/>
-      <c r="K27" s="232"/>
-      <c r="L27" s="232"/>
-      <c r="M27" s="232"/>
-      <c r="N27" s="232"/>
-      <c r="O27" s="233"/>
+      <c r="D27" s="226"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="226"/>
+      <c r="H27" s="226"/>
+      <c r="I27" s="226"/>
+      <c r="J27" s="226"/>
+      <c r="K27" s="226"/>
+      <c r="L27" s="226"/>
+      <c r="M27" s="226"/>
+      <c r="N27" s="226"/>
+      <c r="O27" s="227"/>
     </row>
     <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="217" t="s">
+      <c r="A28" s="231" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="218"/>
-      <c r="C28" s="234" t="str">
+      <c r="B28" s="232"/>
+      <c r="C28" s="259" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,20,)</f>
         <v>Sheikh Zayed</v>
       </c>
-      <c r="D28" s="220"/>
-      <c r="E28" s="220"/>
-      <c r="F28" s="220"/>
-      <c r="G28" s="220"/>
-      <c r="H28" s="220"/>
-      <c r="I28" s="220"/>
-      <c r="J28" s="220"/>
-      <c r="K28" s="220"/>
-      <c r="L28" s="220"/>
-      <c r="M28" s="220"/>
-      <c r="N28" s="220"/>
-      <c r="O28" s="221"/>
+      <c r="D28" s="251"/>
+      <c r="E28" s="251"/>
+      <c r="F28" s="251"/>
+      <c r="G28" s="251"/>
+      <c r="H28" s="251"/>
+      <c r="I28" s="251"/>
+      <c r="J28" s="251"/>
+      <c r="K28" s="251"/>
+      <c r="L28" s="251"/>
+      <c r="M28" s="251"/>
+      <c r="N28" s="251"/>
+      <c r="O28" s="252"/>
     </row>
     <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="33"/>
@@ -17545,10 +17539,10 @@
       <c r="O29" s="36"/>
     </row>
     <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="208" t="s">
+      <c r="A30" s="242" t="s">
         <v>464</v>
       </c>
-      <c r="B30" s="209"/>
+      <c r="B30" s="243"/>
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
@@ -17564,48 +17558,48 @@
       <c r="O30" s="36"/>
     </row>
     <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="210" t="s">
+      <c r="A31" s="260" t="s">
         <v>465</v>
       </c>
-      <c r="B31" s="211"/>
-      <c r="C31" s="212" t="str">
+      <c r="B31" s="261"/>
+      <c r="C31" s="262" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,23,)</f>
         <v>010-00969141</v>
       </c>
-      <c r="D31" s="212"/>
-      <c r="E31" s="212"/>
-      <c r="F31" s="212"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="212"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="212"/>
-      <c r="L31" s="212"/>
-      <c r="M31" s="212"/>
-      <c r="N31" s="212"/>
-      <c r="O31" s="213"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
+      <c r="M31" s="262"/>
+      <c r="N31" s="262"/>
+      <c r="O31" s="263"/>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="254" t="s">
         <v>466</v>
       </c>
-      <c r="B32" s="205"/>
-      <c r="C32" s="227" t="str">
+      <c r="B32" s="255"/>
+      <c r="C32" s="256" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,24,)</f>
         <v>Service Agreement</v>
       </c>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="227"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="227"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
-      <c r="M32" s="227"/>
-      <c r="N32" s="227"/>
-      <c r="O32" s="228"/>
+      <c r="D32" s="256"/>
+      <c r="E32" s="256"/>
+      <c r="F32" s="256"/>
+      <c r="G32" s="256"/>
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="256"/>
+      <c r="L32" s="256"/>
+      <c r="M32" s="256"/>
+      <c r="N32" s="256"/>
+      <c r="O32" s="257"/>
     </row>
     <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33"/>
@@ -17625,10 +17619,10 @@
       <c r="O33" s="44"/>
     </row>
     <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="208" t="s">
+      <c r="A34" s="242" t="s">
         <v>460</v>
       </c>
-      <c r="B34" s="209"/>
+      <c r="B34" s="243"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
@@ -17644,94 +17638,102 @@
       <c r="O34" s="36"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="210"/>
-      <c r="B35" s="211"/>
-      <c r="C35" s="212"/>
-      <c r="D35" s="212"/>
-      <c r="E35" s="212"/>
-      <c r="F35" s="212"/>
-      <c r="G35" s="212"/>
-      <c r="H35" s="212"/>
-      <c r="I35" s="212"/>
-      <c r="J35" s="212"/>
-      <c r="K35" s="212"/>
-      <c r="L35" s="212"/>
-      <c r="M35" s="212"/>
-      <c r="N35" s="212"/>
-      <c r="O35" s="213"/>
+      <c r="A35" s="260"/>
+      <c r="B35" s="261"/>
+      <c r="C35" s="262"/>
+      <c r="D35" s="262"/>
+      <c r="E35" s="262"/>
+      <c r="F35" s="262"/>
+      <c r="G35" s="262"/>
+      <c r="H35" s="262"/>
+      <c r="I35" s="262"/>
+      <c r="J35" s="262"/>
+      <c r="K35" s="262"/>
+      <c r="L35" s="262"/>
+      <c r="M35" s="262"/>
+      <c r="N35" s="262"/>
+      <c r="O35" s="263"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="200"/>
-      <c r="B36" s="201"/>
-      <c r="C36" s="202"/>
-      <c r="D36" s="202"/>
-      <c r="E36" s="202"/>
-      <c r="F36" s="202"/>
-      <c r="G36" s="202"/>
-      <c r="H36" s="202"/>
-      <c r="I36" s="202"/>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="202"/>
-      <c r="M36" s="202"/>
-      <c r="N36" s="202"/>
-      <c r="O36" s="203"/>
+      <c r="A36" s="264"/>
+      <c r="B36" s="265"/>
+      <c r="C36" s="240"/>
+      <c r="D36" s="240"/>
+      <c r="E36" s="240"/>
+      <c r="F36" s="240"/>
+      <c r="G36" s="240"/>
+      <c r="H36" s="240"/>
+      <c r="I36" s="240"/>
+      <c r="J36" s="240"/>
+      <c r="K36" s="240"/>
+      <c r="L36" s="240"/>
+      <c r="M36" s="240"/>
+      <c r="N36" s="240"/>
+      <c r="O36" s="241"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="200"/>
-      <c r="B37" s="201"/>
-      <c r="C37" s="202"/>
-      <c r="D37" s="202"/>
-      <c r="E37" s="202"/>
-      <c r="F37" s="202"/>
-      <c r="G37" s="202"/>
-      <c r="H37" s="202"/>
-      <c r="I37" s="202"/>
-      <c r="J37" s="202"/>
-      <c r="K37" s="202"/>
-      <c r="L37" s="202"/>
-      <c r="M37" s="202"/>
-      <c r="N37" s="202"/>
-      <c r="O37" s="203"/>
+      <c r="A37" s="264"/>
+      <c r="B37" s="265"/>
+      <c r="C37" s="240"/>
+      <c r="D37" s="240"/>
+      <c r="E37" s="240"/>
+      <c r="F37" s="240"/>
+      <c r="G37" s="240"/>
+      <c r="H37" s="240"/>
+      <c r="I37" s="240"/>
+      <c r="J37" s="240"/>
+      <c r="K37" s="240"/>
+      <c r="L37" s="240"/>
+      <c r="M37" s="240"/>
+      <c r="N37" s="240"/>
+      <c r="O37" s="241"/>
     </row>
     <row r="38" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="204"/>
-      <c r="B38" s="205"/>
-      <c r="C38" s="206"/>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="206"/>
-      <c r="I38" s="206"/>
-      <c r="J38" s="206"/>
-      <c r="K38" s="206"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="206"/>
-      <c r="O38" s="207"/>
+      <c r="A38" s="254"/>
+      <c r="B38" s="255"/>
+      <c r="C38" s="233"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
+      <c r="H38" s="233"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:O7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:O37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:O38"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:O35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:O36"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:O23"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:O32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:O27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:O28"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:O31"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:O19"/>
     <mergeCell ref="A20:B20"/>
@@ -17747,33 +17749,25 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:O16"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:O32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:O28"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:O31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:O23"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:O37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:O38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:O35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:O36"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:O7"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/Sheets/SEPEmployees.xlsx
+++ b/Sheets/SEPEmployees.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8368FB0-5010-42FE-8D8E-8E034F8EF5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E40B0A-6B2C-4DBE-B9A2-D2C5E6739C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllOffice" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="630">
   <si>
     <t xml:space="preserve">Khaled Mohamed Helmy Mohamed Yousry Abd Rabo </t>
   </si>
@@ -1878,9 +1878,6 @@
     <t>كريم ايمن محمد عادل</t>
   </si>
   <si>
-    <t>عبد الله عمرو عبد العزيز محمد</t>
-  </si>
-  <si>
     <t>أ/ دعاء عبد الدايم ابراهيم نصار</t>
   </si>
   <si>
@@ -1893,9 +1890,6 @@
     <t>نرمين عصمت محمد حجازى</t>
   </si>
   <si>
-    <t>مروة شريف عبد الحميد سلامه</t>
-  </si>
-  <si>
     <t>احمد سمير حسن السيد</t>
   </si>
   <si>
@@ -1935,9 +1929,6 @@
     <t>نجوى ابراهيم محمود غنيم</t>
   </si>
   <si>
-    <t>حازم ابراهيم عبد الحميد محمد فتاته</t>
-  </si>
-  <si>
     <t>عاصم محمد سعيد عبده</t>
   </si>
   <si>
@@ -2056,6 +2047,18 @@
   </si>
   <si>
     <t>Bar Association Degree (درجة القيد)</t>
+  </si>
+  <si>
+    <t>عبد الله عمرو عبد العزيز محمد حافظ</t>
+  </si>
+  <si>
+    <t>Abd Allah Amr Abd El Aziz Mohamed Hafez</t>
+  </si>
+  <si>
+    <t>مروة شريف عبد الحميد سلامة</t>
+  </si>
+  <si>
+    <t>حازم ابراهيم عبد الحميد محمد فتاتة</t>
   </si>
 </sst>
 </file>
@@ -3522,6 +3525,21 @@
     <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3558,12 +3576,45 @@
     <xf numFmtId="0" fontId="5" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="25" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="25" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3573,38 +3624,158 @@
     <xf numFmtId="165" fontId="25" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="25" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3650,174 +3821,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4324,12 +4327,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD54"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="8" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="1.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="29.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="35.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.21875" style="1" customWidth="1"/>
@@ -4362,7 +4366,7 @@
         <v>67</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>552</v>
@@ -4379,57 +4383,57 @@
       <c r="G1" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="169" t="s">
+      <c r="H1" s="174" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="171"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="176"/>
       <c r="L1" s="76" t="s">
         <v>265</v>
       </c>
-      <c r="M1" s="164" t="s">
-        <v>621</v>
-      </c>
-      <c r="N1" s="166"/>
-      <c r="O1" s="167" t="s">
+      <c r="M1" s="169" t="s">
+        <v>618</v>
+      </c>
+      <c r="N1" s="171"/>
+      <c r="O1" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="168"/>
+      <c r="P1" s="173"/>
       <c r="Q1" s="77" t="s">
         <v>174</v>
       </c>
       <c r="R1" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="164" t="s">
+      <c r="S1" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="T1" s="165"/>
-      <c r="U1" s="166"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="171"/>
       <c r="V1" s="79" t="s">
         <v>82</v>
       </c>
       <c r="W1" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="X1" s="174" t="s">
+      <c r="X1" s="179" t="s">
         <v>208</v>
       </c>
-      <c r="Y1" s="175"/>
-      <c r="Z1" s="174" t="s">
+      <c r="Y1" s="180"/>
+      <c r="Z1" s="179" t="s">
         <v>330</v>
       </c>
-      <c r="AA1" s="175"/>
-      <c r="AB1" s="172" t="s">
+      <c r="AA1" s="180"/>
+      <c r="AB1" s="177" t="s">
         <v>331</v>
       </c>
-      <c r="AC1" s="173"/>
+      <c r="AC1" s="178"/>
       <c r="AD1" s="75" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="67"/>
       <c r="B2" s="68"/>
       <c r="C2" s="68"/>
@@ -4567,7 +4571,7 @@
         <v>400</v>
       </c>
       <c r="W3" s="90" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="X3" s="91" t="s">
         <v>69</v>
@@ -4792,7 +4796,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="159" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E6" s="95" t="s">
         <v>58</v>
@@ -5534,7 +5538,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="120" t="s">
         <v>288</v>
       </c>
@@ -5545,7 +5549,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="134" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E14" s="121" t="s">
         <v>61</v>
@@ -5628,7 +5632,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="120" t="s">
         <v>289</v>
       </c>
@@ -5639,7 +5643,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="134" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E15" s="121" t="s">
         <v>486</v>
@@ -5720,7 +5724,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="120" t="s">
         <v>290</v>
       </c>
@@ -5731,7 +5735,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="134" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E16" s="121" t="s">
         <v>60</v>
@@ -5812,7 +5816,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="120" t="s">
         <v>291</v>
       </c>
@@ -5823,7 +5827,7 @@
         <v>29</v>
       </c>
       <c r="D17" s="134" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E17" s="145" t="s">
         <v>62</v>
@@ -6000,7 +6004,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="120" t="s">
         <v>293</v>
       </c>
@@ -6011,7 +6015,7 @@
         <v>31</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E19" s="121" t="s">
         <v>63</v>
@@ -6282,7 +6286,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="120" t="s">
         <v>489</v>
       </c>
@@ -6376,7 +6380,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="120" t="s">
         <v>496</v>
       </c>
@@ -6387,7 +6391,7 @@
         <v>497</v>
       </c>
       <c r="D23" s="134" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E23" s="121" t="s">
         <v>60</v>
@@ -6520,7 +6524,7 @@
         <v>128</v>
       </c>
       <c r="Q24" s="100" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="R24" s="101">
         <v>45536</v>
@@ -6572,10 +6576,10 @@
         <v>36</v>
       </c>
       <c r="C25" s="153" t="s">
-        <v>544</v>
+        <v>627</v>
       </c>
       <c r="D25" s="159" t="s">
-        <v>569</v>
+        <v>626</v>
       </c>
       <c r="E25" s="95" t="s">
         <v>57</v>
@@ -6614,7 +6618,7 @@
         <v>124</v>
       </c>
       <c r="Q25" s="100" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="R25" s="101">
         <v>45690</v>
@@ -6660,16 +6664,16 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="90" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B26" s="94" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D26" s="159" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E26" s="95" t="s">
         <v>62</v>
@@ -6714,10 +6718,10 @@
         <v>45872</v>
       </c>
       <c r="S26" s="14" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="U26" s="13" t="s">
         <v>132</v>
@@ -6726,7 +6730,7 @@
         <v>429</v>
       </c>
       <c r="W26" s="90" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="X26" s="91" t="s">
         <v>130</v>
@@ -6763,7 +6767,7 @@
         <v>168</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E27" s="95" t="s">
         <v>40</v>
@@ -6858,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="161" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E28" s="95" t="s">
         <v>42</v>
@@ -6953,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="161" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E29" s="95" t="s">
         <v>41</v>
@@ -7037,7 +7041,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="120" t="s">
         <v>298</v>
       </c>
@@ -7048,7 +7052,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="134" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E30" s="121" t="s">
         <v>43</v>
@@ -7142,7 +7146,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="162" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E31" s="95" t="s">
         <v>44</v>
@@ -7237,7 +7241,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="161" t="s">
-        <v>574</v>
+        <v>628</v>
       </c>
       <c r="E32" s="95" t="s">
         <v>43</v>
@@ -7321,7 +7325,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="120" t="s">
         <v>301</v>
       </c>
@@ -7332,7 +7336,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="121" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E33" s="121" t="s">
         <v>45</v>
@@ -7427,7 +7431,7 @@
         <v>33</v>
       </c>
       <c r="D34" s="161" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E34" s="95" t="s">
         <v>56</v>
@@ -7522,7 +7526,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="161" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E35" s="95" t="s">
         <v>46</v>
@@ -7617,7 +7621,7 @@
         <v>7</v>
       </c>
       <c r="D36" s="161" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E36" s="95" t="s">
         <v>47</v>
@@ -7712,7 +7716,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="161" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E37" s="95" t="s">
         <v>48</v>
@@ -7802,10 +7806,10 @@
         <v>37</v>
       </c>
       <c r="C38" s="157" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D38" s="163" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E38" s="95" t="s">
         <v>49</v>
@@ -7900,7 +7904,7 @@
         <v>55</v>
       </c>
       <c r="D39" s="161" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E39" s="95" t="s">
         <v>50</v>
@@ -7995,7 +7999,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="161" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E40" s="95" t="s">
         <v>51</v>
@@ -8090,7 +8094,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="161" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E41" s="95" t="s">
         <v>52</v>
@@ -8185,7 +8189,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="161" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E42" s="95" t="s">
         <v>52</v>
@@ -8269,7 +8273,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="120" t="s">
         <v>311</v>
       </c>
@@ -8280,7 +8284,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="121" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E43" s="121" t="s">
         <v>551</v>
@@ -8374,7 +8378,7 @@
         <v>514</v>
       </c>
       <c r="D44" s="163" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E44" s="95" t="s">
         <v>53</v>
@@ -8469,7 +8473,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="163" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E45" s="95" t="s">
         <v>54</v>
@@ -8564,7 +8568,7 @@
         <v>164</v>
       </c>
       <c r="D46" s="163" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E46" s="95" t="s">
         <v>475</v>
@@ -8648,7 +8652,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="120" t="s">
         <v>471</v>
       </c>
@@ -8659,7 +8663,7 @@
         <v>472</v>
       </c>
       <c r="D47" s="138" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E47" s="121" t="s">
         <v>417</v>
@@ -8740,7 +8744,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="120" t="s">
         <v>504</v>
       </c>
@@ -8751,7 +8755,7 @@
         <v>515</v>
       </c>
       <c r="D48" s="138" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E48" s="121" t="s">
         <v>505</v>
@@ -8846,7 +8850,7 @@
         <v>524</v>
       </c>
       <c r="D49" s="163" t="s">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="E49" s="95" t="s">
         <v>516</v>
@@ -8941,7 +8945,7 @@
         <v>538</v>
       </c>
       <c r="D50" s="163" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E50" s="95" t="s">
         <v>527</v>
@@ -9027,16 +9031,16 @@
     </row>
     <row r="51" spans="1:30" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="90" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B51" s="94" t="s">
         <v>37</v>
       </c>
       <c r="C51" s="157" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D51" s="163" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E51" s="95" t="s">
         <v>45</v>
@@ -9048,16 +9052,16 @@
         <v>35128</v>
       </c>
       <c r="H51" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="J51" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="I51" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>617</v>
-      </c>
       <c r="K51" s="17" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="L51" s="15">
         <v>69654522</v>
@@ -9081,7 +9085,7 @@
         <v>46012</v>
       </c>
       <c r="S51" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="T51" s="11" t="s">
         <v>159</v>
@@ -9093,7 +9097,7 @@
         <v>437</v>
       </c>
       <c r="W51" s="90" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="X51" s="91" t="s">
         <v>258</v>
@@ -9217,6 +9221,11 @@
     <filterColumn colId="23" showButton="0"/>
     <filterColumn colId="25" showButton="0"/>
     <filterColumn colId="27" showButton="0"/>
+    <filterColumn colId="29">
+      <filters>
+        <filter val="Active"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="S1:U1"/>
@@ -9276,10 +9285,10 @@
       <c r="A3" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="185" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="184"/>
+      <c r="C3" s="186"/>
       <c r="D3" s="49">
         <v>46219</v>
       </c>
@@ -9450,10 +9459,10 @@
       <c r="A18" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="176" t="s">
+      <c r="B18" s="183" t="s">
         <v>379</v>
       </c>
-      <c r="C18" s="177"/>
+      <c r="C18" s="184"/>
       <c r="D18" s="49">
         <v>46042</v>
       </c>
@@ -9624,10 +9633,10 @@
       <c r="A33" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="B33" s="176" t="s">
+      <c r="B33" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="177"/>
+      <c r="C33" s="184"/>
       <c r="D33" s="49">
         <v>46126</v>
       </c>
@@ -9756,21 +9765,21 @@
       <c r="A45" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="B45" s="185" t="s">
+      <c r="B45" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="186"/>
+      <c r="C45" s="188"/>
       <c r="D45" s="59">
         <v>45274</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="189" t="s">
+      <c r="A46" s="191" t="s">
         <v>385</v>
       </c>
-      <c r="B46" s="190"/>
-      <c r="C46" s="190"/>
-      <c r="D46" s="191"/>
+      <c r="B46" s="192"/>
+      <c r="C46" s="192"/>
+      <c r="D46" s="193"/>
     </row>
     <row r="47" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="60">
@@ -9838,10 +9847,10 @@
       <c r="A52" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="B52" s="176" t="s">
+      <c r="B52" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="177"/>
+      <c r="C52" s="184"/>
       <c r="D52" s="49">
         <v>46162</v>
       </c>
@@ -9972,10 +9981,10 @@
       <c r="A64" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="B64" s="176" t="s">
+      <c r="B64" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C64" s="177"/>
+      <c r="C64" s="184"/>
       <c r="D64" s="49">
         <v>46090</v>
       </c>
@@ -10086,10 +10095,10 @@
       <c r="A74" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="176" t="s">
+      <c r="B74" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="177"/>
+      <c r="C74" s="184"/>
       <c r="D74" s="49">
         <v>46053</v>
       </c>
@@ -10172,10 +10181,10 @@
       <c r="A82" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="187" t="s">
+      <c r="B82" s="189" t="s">
         <v>33</v>
       </c>
-      <c r="C82" s="188"/>
+      <c r="C82" s="190"/>
       <c r="D82" s="49">
         <v>46314</v>
       </c>
@@ -10334,10 +10343,10 @@
       <c r="A96" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="B96" s="176" t="s">
+      <c r="B96" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C96" s="177"/>
+      <c r="C96" s="184"/>
       <c r="D96" s="49">
         <v>46049</v>
       </c>
@@ -10480,10 +10489,10 @@
       <c r="A109" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="176" t="s">
+      <c r="B109" s="183" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="177"/>
+      <c r="C109" s="184"/>
       <c r="D109" s="49">
         <v>46190</v>
       </c>
@@ -10562,10 +10571,10 @@
       <c r="A116" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="B116" s="176" t="s">
+      <c r="B116" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="C116" s="177"/>
+      <c r="C116" s="184"/>
       <c r="D116" s="49">
         <v>46022</v>
       </c>
@@ -10748,10 +10757,10 @@
       <c r="A132" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="B132" s="176" t="s">
+      <c r="B132" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="177"/>
+      <c r="C132" s="184"/>
       <c r="D132" s="49">
         <v>46203</v>
       </c>
@@ -10910,10 +10919,10 @@
       <c r="A146" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="176" t="s">
+      <c r="B146" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="C146" s="177"/>
+      <c r="C146" s="184"/>
       <c r="D146" s="49">
         <v>46217</v>
       </c>
@@ -11096,10 +11105,10 @@
       <c r="A162" s="47" t="s">
         <v>308</v>
       </c>
-      <c r="B162" s="176" t="s">
+      <c r="B162" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="177"/>
+      <c r="C162" s="184"/>
       <c r="D162" s="49">
         <v>46340</v>
       </c>
@@ -11330,10 +11339,10 @@
       <c r="A182" s="47" t="s">
         <v>309</v>
       </c>
-      <c r="B182" s="176" t="s">
+      <c r="B182" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="C182" s="177"/>
+      <c r="C182" s="184"/>
       <c r="D182" s="49">
         <v>46202</v>
       </c>
@@ -11516,10 +11525,10 @@
       <c r="A198" s="47" t="s">
         <v>310</v>
       </c>
-      <c r="B198" s="176" t="s">
+      <c r="B198" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="C198" s="177"/>
+      <c r="C198" s="184"/>
       <c r="D198" s="49">
         <v>46345</v>
       </c>
@@ -11656,10 +11665,10 @@
       <c r="A210" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="B210" s="176" t="s">
+      <c r="B210" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="C210" s="177"/>
+      <c r="C210" s="184"/>
       <c r="D210" s="49">
         <v>46222</v>
       </c>
@@ -11758,10 +11767,10 @@
       <c r="A219" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="B219" s="176" t="s">
+      <c r="B219" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C219" s="177"/>
+      <c r="C219" s="184"/>
       <c r="D219" s="49">
         <v>46084</v>
       </c>
@@ -11814,10 +11823,10 @@
       <c r="A224" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="B224" s="176" t="s">
+      <c r="B224" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C224" s="177"/>
+      <c r="C224" s="184"/>
       <c r="D224" s="49">
         <v>46006</v>
       </c>
@@ -11874,10 +11883,10 @@
       <c r="A230" s="55" t="s">
         <v>286</v>
       </c>
-      <c r="B230" s="176" t="s">
+      <c r="B230" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="C230" s="177"/>
+      <c r="C230" s="184"/>
       <c r="D230" s="49">
         <v>46203</v>
       </c>
@@ -11964,21 +11973,21 @@
       <c r="A238" s="55" t="s">
         <v>471</v>
       </c>
-      <c r="B238" s="176" t="s">
+      <c r="B238" s="183" t="s">
         <v>472</v>
       </c>
-      <c r="C238" s="177"/>
+      <c r="C238" s="184"/>
       <c r="D238" s="49">
         <v>45460</v>
       </c>
     </row>
     <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="178" t="s">
+      <c r="A239" s="194" t="s">
         <v>385</v>
       </c>
-      <c r="B239" s="179"/>
-      <c r="C239" s="179"/>
-      <c r="D239" s="180"/>
+      <c r="B239" s="195"/>
+      <c r="C239" s="195"/>
+      <c r="D239" s="196"/>
     </row>
     <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="44">
@@ -11998,21 +12007,21 @@
       <c r="A241" s="55" t="s">
         <v>504</v>
       </c>
-      <c r="B241" s="176" t="s">
+      <c r="B241" s="183" t="s">
         <v>509</v>
       </c>
-      <c r="C241" s="177"/>
+      <c r="C241" s="184"/>
       <c r="D241" s="49">
         <v>45579</v>
       </c>
     </row>
     <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="178" t="s">
+      <c r="A242" s="194" t="s">
         <v>385</v>
       </c>
-      <c r="B242" s="179"/>
-      <c r="C242" s="179"/>
-      <c r="D242" s="180"/>
+      <c r="B242" s="195"/>
+      <c r="C242" s="195"/>
+      <c r="D242" s="196"/>
     </row>
     <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="44">
@@ -12032,10 +12041,10 @@
       <c r="A244" s="55" t="s">
         <v>513</v>
       </c>
-      <c r="B244" s="176" t="s">
+      <c r="B244" s="183" t="s">
         <v>523</v>
       </c>
-      <c r="C244" s="177"/>
+      <c r="C244" s="184"/>
       <c r="D244" s="49">
         <v>46167</v>
       </c>
@@ -12088,10 +12097,10 @@
       <c r="A249" s="55" t="s">
         <v>526</v>
       </c>
-      <c r="B249" s="176" t="s">
+      <c r="B249" s="183" t="s">
         <v>528</v>
       </c>
-      <c r="C249" s="177"/>
+      <c r="C249" s="184"/>
       <c r="D249" s="49">
         <v>46234</v>
       </c>
@@ -12142,12 +12151,12 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="55" t="s">
-        <v>610</v>
-      </c>
-      <c r="B254" s="176" t="s">
-        <v>611</v>
-      </c>
-      <c r="C254" s="177"/>
+        <v>607</v>
+      </c>
+      <c r="B254" s="183" t="s">
+        <v>608</v>
+      </c>
+      <c r="C254" s="184"/>
       <c r="D254" s="49">
         <v>46194</v>
       </c>
@@ -12174,21 +12183,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B109:C109"/>
     <mergeCell ref="B254:C254"/>
     <mergeCell ref="B146:C146"/>
     <mergeCell ref="B162:C162"/>
@@ -12205,6 +12199,21 @@
     <mergeCell ref="A239:D239"/>
     <mergeCell ref="A242:D242"/>
     <mergeCell ref="B249:C249"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B109:C109"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="timePeriod" dxfId="24" priority="34" timePeriod="nextWeek">
@@ -12358,7 +12367,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B1" s="108" t="s">
         <v>34</v>
@@ -13558,10 +13567,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="117" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B25" s="119" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>320</v>
@@ -14161,7 +14170,7 @@
         <v>306</v>
       </c>
       <c r="B37" s="105" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>320</v>
@@ -14808,10 +14817,10 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="117" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B50" s="105" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>320</v>
@@ -14882,38 +14891,38 @@
     <col min="11" max="12" width="15.77734375" style="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="262" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="258" t="s">
+    <row r="1" spans="1:12" s="168" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="164" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="259" t="s">
+      <c r="B1" s="165" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="259" t="s">
+      <c r="C1" s="165" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="259" t="s">
+      <c r="D1" s="165" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="259" t="s">
+      <c r="E1" s="165" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1" s="165" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="166" t="s">
+        <v>622</v>
+      </c>
+      <c r="H1" s="166" t="s">
+        <v>623</v>
+      </c>
+      <c r="I1" s="166" t="s">
         <v>624</v>
       </c>
-      <c r="F1" s="259" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="260" t="s">
+      <c r="J1" s="166" t="s">
         <v>625</v>
       </c>
-      <c r="H1" s="260" t="s">
-        <v>626</v>
-      </c>
-      <c r="I1" s="260" t="s">
-        <v>627</v>
-      </c>
-      <c r="J1" s="260" t="s">
-        <v>628</v>
-      </c>
-      <c r="K1" s="261" t="s">
+      <c r="K1" s="167" t="s">
         <v>65</v>
       </c>
       <c r="L1" s="52" t="s">
@@ -16920,49 +16929,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="248" t="s">
         <v>373</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="194"/>
+      <c r="B1" s="249"/>
+      <c r="C1" s="249"/>
+      <c r="D1" s="249"/>
+      <c r="E1" s="249"/>
+      <c r="F1" s="249"/>
+      <c r="G1" s="249"/>
+      <c r="H1" s="249"/>
+      <c r="I1" s="249"/>
+      <c r="J1" s="249"/>
+      <c r="K1" s="249"/>
+      <c r="L1" s="249"/>
+      <c r="M1" s="249"/>
+      <c r="N1" s="249"/>
+      <c r="O1" s="250"/>
     </row>
     <row r="2" spans="1:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="251" t="s">
         <v>496</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="197" t="s">
+      <c r="C2" s="251"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="198"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="200" t="str">
+      <c r="G2" s="254"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="256" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,2,)</f>
         <v>Lawyer</v>
       </c>
-      <c r="J2" s="201"/>
-      <c r="K2" s="201"/>
-      <c r="L2" s="201"/>
-      <c r="M2" s="201"/>
-      <c r="N2" s="201"/>
-      <c r="O2" s="202"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="257"/>
+      <c r="L2" s="257"/>
+      <c r="M2" s="257"/>
+      <c r="N2" s="257"/>
+      <c r="O2" s="258"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="33"/>
@@ -16982,18 +16991,18 @@
       <c r="O3" s="38"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="203" t="s">
+      <c r="A4" s="259" t="s">
         <v>461</v>
       </c>
-      <c r="B4" s="204"/>
+      <c r="B4" s="260"/>
       <c r="C4" s="30"/>
       <c r="D4" s="39"/>
       <c r="E4" s="39"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="206"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
       <c r="K4" s="31"/>
       <c r="L4" s="31"/>
       <c r="M4" s="31"/>
@@ -17001,136 +17010,136 @@
       <c r="O4" s="40"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="219" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209" t="str">
+      <c r="B5" s="220"/>
+      <c r="C5" s="242" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,3,)</f>
         <v>Hussien Sherif Mohamed Monier Amer</v>
       </c>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="210"/>
-      <c r="K5" s="210"/>
-      <c r="L5" s="210"/>
-      <c r="M5" s="210"/>
-      <c r="N5" s="210"/>
-      <c r="O5" s="211"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
+      <c r="O5" s="244"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="226" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="214" t="str">
+      <c r="B6" s="227"/>
+      <c r="C6" s="245" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,17,)</f>
         <v>-</v>
       </c>
-      <c r="D6" s="215"/>
-      <c r="E6" s="215"/>
-      <c r="F6" s="215"/>
-      <c r="G6" s="215"/>
-      <c r="H6" s="215"/>
-      <c r="I6" s="215"/>
-      <c r="J6" s="215"/>
-      <c r="K6" s="215"/>
-      <c r="L6" s="215"/>
-      <c r="M6" s="215"/>
-      <c r="N6" s="215"/>
-      <c r="O6" s="216"/>
+      <c r="D6" s="246"/>
+      <c r="E6" s="246"/>
+      <c r="F6" s="246"/>
+      <c r="G6" s="246"/>
+      <c r="H6" s="246"/>
+      <c r="I6" s="246"/>
+      <c r="J6" s="246"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="246"/>
+      <c r="M6" s="246"/>
+      <c r="N6" s="246"/>
+      <c r="O6" s="247"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="226" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="213"/>
-      <c r="C7" s="217" t="str">
+      <c r="B7" s="227"/>
+      <c r="C7" s="238" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,4,)</f>
         <v>حسين شريف محمد منير عامر</v>
       </c>
-      <c r="D7" s="218"/>
-      <c r="E7" s="218"/>
-      <c r="F7" s="218"/>
-      <c r="G7" s="218"/>
-      <c r="H7" s="218"/>
-      <c r="I7" s="218"/>
-      <c r="J7" s="218"/>
-      <c r="K7" s="218"/>
-      <c r="L7" s="218"/>
-      <c r="M7" s="218"/>
-      <c r="N7" s="218"/>
-      <c r="O7" s="219"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="229"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229"/>
+      <c r="K7" s="229"/>
+      <c r="L7" s="229"/>
+      <c r="M7" s="229"/>
+      <c r="N7" s="229"/>
+      <c r="O7" s="230"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="212" t="s">
+      <c r="A8" s="226" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="213"/>
-      <c r="C8" s="217" t="str">
+      <c r="B8" s="227"/>
+      <c r="C8" s="238" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,5,)</f>
         <v xml:space="preserve">Associate </v>
       </c>
-      <c r="D8" s="218"/>
-      <c r="E8" s="218"/>
-      <c r="F8" s="218"/>
-      <c r="G8" s="218"/>
-      <c r="H8" s="218"/>
-      <c r="I8" s="218"/>
-      <c r="J8" s="218"/>
-      <c r="K8" s="218"/>
-      <c r="L8" s="218"/>
-      <c r="M8" s="218"/>
-      <c r="N8" s="218"/>
-      <c r="O8" s="219"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="230"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="212" t="s">
+      <c r="A9" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="213"/>
-      <c r="C9" s="220" t="str">
+      <c r="B9" s="227"/>
+      <c r="C9" s="239" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,6,)</f>
         <v>Banking &amp; Procedures</v>
       </c>
-      <c r="D9" s="221"/>
-      <c r="E9" s="221"/>
-      <c r="F9" s="221"/>
-      <c r="G9" s="221"/>
-      <c r="H9" s="221"/>
-      <c r="I9" s="221"/>
-      <c r="J9" s="221"/>
-      <c r="K9" s="221"/>
-      <c r="L9" s="221"/>
-      <c r="M9" s="221"/>
-      <c r="N9" s="221"/>
-      <c r="O9" s="222"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="240"/>
+      <c r="I9" s="240"/>
+      <c r="J9" s="240"/>
+      <c r="K9" s="240"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="240"/>
+      <c r="N9" s="240"/>
+      <c r="O9" s="241"/>
     </row>
     <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="223" t="s">
+      <c r="A10" s="214" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="224"/>
-      <c r="C10" s="225">
+      <c r="B10" s="215"/>
+      <c r="C10" s="203">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,22,)</f>
         <v>406</v>
       </c>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="225"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="225"/>
-      <c r="N10" s="225"/>
-      <c r="O10" s="226"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="203"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="203"/>
+      <c r="K10" s="203"/>
+      <c r="L10" s="203"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="204"/>
     </row>
     <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29"/>
@@ -17150,111 +17159,111 @@
       <c r="O11" s="32"/>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="234" t="s">
+      <c r="A12" s="205" t="s">
         <v>454</v>
       </c>
-      <c r="B12" s="235"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="236"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="237"/>
+      <c r="B12" s="206"/>
+      <c r="C12" s="235"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235"/>
+      <c r="L12" s="235"/>
+      <c r="M12" s="235"/>
+      <c r="N12" s="235"/>
+      <c r="O12" s="236"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="207" t="s">
+      <c r="A13" s="219" t="s">
         <v>455</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="238">
+      <c r="B13" s="220"/>
+      <c r="C13" s="237">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,7,)</f>
         <v>35383</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
-      <c r="M13" s="239"/>
-      <c r="N13" s="239"/>
-      <c r="O13" s="240"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="222"/>
+      <c r="G13" s="222"/>
+      <c r="H13" s="222"/>
+      <c r="I13" s="222"/>
+      <c r="J13" s="222"/>
+      <c r="K13" s="222"/>
+      <c r="L13" s="222"/>
+      <c r="M13" s="222"/>
+      <c r="N13" s="222"/>
+      <c r="O13" s="223"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="212" t="s">
+      <c r="A14" s="226" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="217" t="str">
+      <c r="B14" s="227"/>
+      <c r="C14" s="238" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,8,)</f>
         <v>Master of Laws</v>
       </c>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
-      <c r="F14" s="218"/>
-      <c r="G14" s="218"/>
-      <c r="H14" s="218"/>
-      <c r="I14" s="218"/>
-      <c r="J14" s="218"/>
-      <c r="K14" s="218"/>
-      <c r="L14" s="218"/>
-      <c r="M14" s="218"/>
-      <c r="N14" s="218"/>
-      <c r="O14" s="219"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="229"/>
+      <c r="I14" s="229"/>
+      <c r="J14" s="229"/>
+      <c r="K14" s="229"/>
+      <c r="L14" s="229"/>
+      <c r="M14" s="229"/>
+      <c r="N14" s="229"/>
+      <c r="O14" s="230"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="230" t="s">
+      <c r="A15" s="211" t="s">
         <v>456</v>
       </c>
-      <c r="B15" s="231"/>
-      <c r="C15" s="241" t="str">
+      <c r="B15" s="212"/>
+      <c r="C15" s="213" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,9,)</f>
         <v>Professional Legal Practice</v>
       </c>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="232"/>
-      <c r="G15" s="232"/>
-      <c r="H15" s="232"/>
-      <c r="I15" s="232"/>
-      <c r="J15" s="232"/>
-      <c r="K15" s="232"/>
-      <c r="L15" s="232"/>
-      <c r="M15" s="232"/>
-      <c r="N15" s="232"/>
-      <c r="O15" s="233"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="199"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="199"/>
+      <c r="K15" s="199"/>
+      <c r="L15" s="199"/>
+      <c r="M15" s="199"/>
+      <c r="N15" s="199"/>
+      <c r="O15" s="200"/>
     </row>
     <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="223" t="s">
+      <c r="A16" s="214" t="s">
         <v>463</v>
       </c>
-      <c r="B16" s="224"/>
-      <c r="C16" s="242" t="str">
+      <c r="B16" s="215"/>
+      <c r="C16" s="216" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,10,)</f>
         <v>University of Law</v>
       </c>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="243"/>
-      <c r="J16" s="243"/>
-      <c r="K16" s="243"/>
-      <c r="L16" s="243"/>
-      <c r="M16" s="243"/>
-      <c r="N16" s="243"/>
-      <c r="O16" s="244"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="217"/>
+      <c r="F16" s="217"/>
+      <c r="G16" s="217"/>
+      <c r="H16" s="217"/>
+      <c r="I16" s="217"/>
+      <c r="J16" s="217"/>
+      <c r="K16" s="217"/>
+      <c r="L16" s="217"/>
+      <c r="M16" s="217"/>
+      <c r="N16" s="217"/>
+      <c r="O16" s="218"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="29"/>
@@ -17274,10 +17283,10 @@
       <c r="O17" s="32"/>
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="234" t="s">
+      <c r="A18" s="205" t="s">
         <v>462</v>
       </c>
-      <c r="B18" s="235"/>
+      <c r="B18" s="206"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
@@ -17293,114 +17302,114 @@
       <c r="O18" s="32"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="207" t="s">
+      <c r="A19" s="219" t="s">
         <v>376</v>
       </c>
-      <c r="B19" s="208"/>
-      <c r="C19" s="227" t="str">
+      <c r="B19" s="220"/>
+      <c r="C19" s="232" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,12,)</f>
         <v>-</v>
       </c>
-      <c r="D19" s="228"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="228"/>
-      <c r="G19" s="228"/>
-      <c r="H19" s="228"/>
-      <c r="I19" s="228"/>
-      <c r="J19" s="228"/>
-      <c r="K19" s="228"/>
-      <c r="L19" s="228"/>
-      <c r="M19" s="228"/>
-      <c r="N19" s="228"/>
-      <c r="O19" s="229"/>
+      <c r="D19" s="233"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="233"/>
+      <c r="G19" s="233"/>
+      <c r="H19" s="233"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="233"/>
+      <c r="K19" s="233"/>
+      <c r="L19" s="233"/>
+      <c r="M19" s="233"/>
+      <c r="N19" s="233"/>
+      <c r="O19" s="234"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="230" t="s">
+      <c r="A20" s="211" t="s">
         <v>457</v>
       </c>
-      <c r="B20" s="231"/>
-      <c r="C20" s="232">
+      <c r="B20" s="212"/>
+      <c r="C20" s="199">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,14,)</f>
         <v>47469</v>
       </c>
-      <c r="D20" s="232"/>
-      <c r="E20" s="232"/>
-      <c r="F20" s="232"/>
-      <c r="G20" s="232"/>
-      <c r="H20" s="232"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
-      <c r="K20" s="232"/>
-      <c r="L20" s="232"/>
-      <c r="M20" s="232"/>
-      <c r="N20" s="232"/>
-      <c r="O20" s="233"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="199"/>
+      <c r="F20" s="199"/>
+      <c r="G20" s="199"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="199"/>
+      <c r="L20" s="199"/>
+      <c r="M20" s="199"/>
+      <c r="N20" s="199"/>
+      <c r="O20" s="200"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="230" t="s">
+      <c r="A21" s="211" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="231"/>
-      <c r="C21" s="241">
+      <c r="B21" s="212"/>
+      <c r="C21" s="213">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,15,)</f>
         <v>710391</v>
       </c>
-      <c r="D21" s="232"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="232"/>
-      <c r="G21" s="232"/>
-      <c r="H21" s="232"/>
-      <c r="I21" s="232"/>
-      <c r="J21" s="232"/>
-      <c r="K21" s="232"/>
-      <c r="L21" s="232"/>
-      <c r="M21" s="232"/>
-      <c r="N21" s="232"/>
-      <c r="O21" s="233"/>
+      <c r="D21" s="199"/>
+      <c r="E21" s="199"/>
+      <c r="F21" s="199"/>
+      <c r="G21" s="199"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="199"/>
+      <c r="L21" s="199"/>
+      <c r="M21" s="199"/>
+      <c r="N21" s="199"/>
+      <c r="O21" s="200"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="230" t="s">
+      <c r="A22" s="211" t="s">
         <v>458</v>
       </c>
-      <c r="B22" s="231"/>
-      <c r="C22" s="241" t="str">
+      <c r="B22" s="212"/>
+      <c r="C22" s="213" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,16,)</f>
         <v>جدول عام</v>
       </c>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
-      <c r="M22" s="232"/>
-      <c r="N22" s="232"/>
-      <c r="O22" s="233"/>
+      <c r="D22" s="199"/>
+      <c r="E22" s="199"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="199"/>
+      <c r="N22" s="199"/>
+      <c r="O22" s="200"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="223" t="s">
+      <c r="A23" s="214" t="s">
         <v>265</v>
       </c>
-      <c r="B23" s="224"/>
-      <c r="C23" s="242" t="str">
+      <c r="B23" s="215"/>
+      <c r="C23" s="216" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,11,)</f>
         <v>2021</v>
       </c>
-      <c r="D23" s="243"/>
-      <c r="E23" s="243"/>
-      <c r="F23" s="243"/>
-      <c r="G23" s="243"/>
-      <c r="H23" s="243"/>
-      <c r="I23" s="243"/>
-      <c r="J23" s="243"/>
-      <c r="K23" s="243"/>
-      <c r="L23" s="243"/>
-      <c r="M23" s="243"/>
-      <c r="N23" s="243"/>
-      <c r="O23" s="244"/>
+      <c r="D23" s="217"/>
+      <c r="E23" s="217"/>
+      <c r="F23" s="217"/>
+      <c r="G23" s="217"/>
+      <c r="H23" s="217"/>
+      <c r="I23" s="217"/>
+      <c r="J23" s="217"/>
+      <c r="K23" s="217"/>
+      <c r="L23" s="217"/>
+      <c r="M23" s="217"/>
+      <c r="N23" s="217"/>
+      <c r="O23" s="218"/>
     </row>
     <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="29"/>
@@ -17420,10 +17429,10 @@
       <c r="O24" s="32"/>
     </row>
     <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="234" t="s">
+      <c r="A25" s="205" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="235"/>
+      <c r="B25" s="206"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
@@ -17439,70 +17448,70 @@
       <c r="O25" s="32"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="219" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="208"/>
-      <c r="C26" s="245">
+      <c r="B26" s="220"/>
+      <c r="C26" s="221">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,18,)</f>
         <v>45397</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
-      <c r="M26" s="239"/>
-      <c r="N26" s="239"/>
-      <c r="O26" s="240"/>
+      <c r="D26" s="222"/>
+      <c r="E26" s="222"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="222"/>
+      <c r="H26" s="222"/>
+      <c r="I26" s="222"/>
+      <c r="J26" s="222"/>
+      <c r="K26" s="222"/>
+      <c r="L26" s="222"/>
+      <c r="M26" s="222"/>
+      <c r="N26" s="222"/>
+      <c r="O26" s="223"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="212" t="s">
+      <c r="A27" s="226" t="s">
         <v>459</v>
       </c>
-      <c r="B27" s="213"/>
-      <c r="C27" s="250" t="str">
+      <c r="B27" s="227"/>
+      <c r="C27" s="228" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,19,)</f>
         <v>Villa 26 Telal Al Guziera</v>
       </c>
-      <c r="D27" s="218"/>
-      <c r="E27" s="218"/>
-      <c r="F27" s="218"/>
-      <c r="G27" s="218"/>
-      <c r="H27" s="218"/>
-      <c r="I27" s="218"/>
-      <c r="J27" s="218"/>
-      <c r="K27" s="218"/>
-      <c r="L27" s="218"/>
-      <c r="M27" s="218"/>
-      <c r="N27" s="218"/>
-      <c r="O27" s="219"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="229"/>
+      <c r="I27" s="229"/>
+      <c r="J27" s="229"/>
+      <c r="K27" s="229"/>
+      <c r="L27" s="229"/>
+      <c r="M27" s="229"/>
+      <c r="N27" s="229"/>
+      <c r="O27" s="230"/>
     </row>
     <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="223" t="s">
+      <c r="A28" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="224"/>
-      <c r="C28" s="251" t="str">
+      <c r="B28" s="215"/>
+      <c r="C28" s="231" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,20,)</f>
         <v>Sheikh Zayed</v>
       </c>
-      <c r="D28" s="243"/>
-      <c r="E28" s="243"/>
-      <c r="F28" s="243"/>
-      <c r="G28" s="243"/>
-      <c r="H28" s="243"/>
-      <c r="I28" s="243"/>
-      <c r="J28" s="243"/>
-      <c r="K28" s="243"/>
-      <c r="L28" s="243"/>
-      <c r="M28" s="243"/>
-      <c r="N28" s="243"/>
-      <c r="O28" s="244"/>
+      <c r="D28" s="217"/>
+      <c r="E28" s="217"/>
+      <c r="F28" s="217"/>
+      <c r="G28" s="217"/>
+      <c r="H28" s="217"/>
+      <c r="I28" s="217"/>
+      <c r="J28" s="217"/>
+      <c r="K28" s="217"/>
+      <c r="L28" s="217"/>
+      <c r="M28" s="217"/>
+      <c r="N28" s="217"/>
+      <c r="O28" s="218"/>
     </row>
     <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="29"/>
@@ -17522,10 +17531,10 @@
       <c r="O29" s="32"/>
     </row>
     <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="234" t="s">
+      <c r="A30" s="205" t="s">
         <v>464</v>
       </c>
-      <c r="B30" s="235"/>
+      <c r="B30" s="206"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
@@ -17541,48 +17550,48 @@
       <c r="O30" s="32"/>
     </row>
     <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="252" t="s">
+      <c r="A31" s="207" t="s">
         <v>465</v>
       </c>
-      <c r="B31" s="253"/>
-      <c r="C31" s="254" t="str">
+      <c r="B31" s="208"/>
+      <c r="C31" s="209" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,23,)</f>
         <v>010-00969141</v>
       </c>
-      <c r="D31" s="254"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="254"/>
-      <c r="G31" s="254"/>
-      <c r="H31" s="254"/>
-      <c r="I31" s="254"/>
-      <c r="J31" s="254"/>
-      <c r="K31" s="254"/>
-      <c r="L31" s="254"/>
-      <c r="M31" s="254"/>
-      <c r="N31" s="254"/>
-      <c r="O31" s="255"/>
+      <c r="D31" s="209"/>
+      <c r="E31" s="209"/>
+      <c r="F31" s="209"/>
+      <c r="G31" s="209"/>
+      <c r="H31" s="209"/>
+      <c r="I31" s="209"/>
+      <c r="J31" s="209"/>
+      <c r="K31" s="209"/>
+      <c r="L31" s="209"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="209"/>
+      <c r="O31" s="210"/>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="246" t="s">
+      <c r="A32" s="201" t="s">
         <v>466</v>
       </c>
-      <c r="B32" s="247"/>
-      <c r="C32" s="248" t="str">
+      <c r="B32" s="202"/>
+      <c r="C32" s="224" t="str">
         <f>VLOOKUP(B2,AllOffice!A1:AD1005,24,)</f>
         <v>Service Agreement</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="E32" s="248"/>
-      <c r="F32" s="248"/>
-      <c r="G32" s="248"/>
-      <c r="H32" s="248"/>
-      <c r="I32" s="248"/>
-      <c r="J32" s="248"/>
-      <c r="K32" s="248"/>
-      <c r="L32" s="248"/>
-      <c r="M32" s="248"/>
-      <c r="N32" s="248"/>
-      <c r="O32" s="249"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
+      <c r="M32" s="224"/>
+      <c r="N32" s="224"/>
+      <c r="O32" s="225"/>
     </row>
     <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29"/>
@@ -17602,10 +17611,10 @@
       <c r="O33" s="40"/>
     </row>
     <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="234" t="s">
+      <c r="A34" s="205" t="s">
         <v>460</v>
       </c>
-      <c r="B34" s="235"/>
+      <c r="B34" s="206"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
@@ -17621,102 +17630,94 @@
       <c r="O34" s="32"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="252"/>
-      <c r="B35" s="253"/>
-      <c r="C35" s="254"/>
-      <c r="D35" s="254"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="254"/>
-      <c r="G35" s="254"/>
-      <c r="H35" s="254"/>
-      <c r="I35" s="254"/>
-      <c r="J35" s="254"/>
-      <c r="K35" s="254"/>
-      <c r="L35" s="254"/>
-      <c r="M35" s="254"/>
-      <c r="N35" s="254"/>
-      <c r="O35" s="255"/>
+      <c r="A35" s="207"/>
+      <c r="B35" s="208"/>
+      <c r="C35" s="209"/>
+      <c r="D35" s="209"/>
+      <c r="E35" s="209"/>
+      <c r="F35" s="209"/>
+      <c r="G35" s="209"/>
+      <c r="H35" s="209"/>
+      <c r="I35" s="209"/>
+      <c r="J35" s="209"/>
+      <c r="K35" s="209"/>
+      <c r="L35" s="209"/>
+      <c r="M35" s="209"/>
+      <c r="N35" s="209"/>
+      <c r="O35" s="210"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="256"/>
-      <c r="B36" s="257"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="232"/>
-      <c r="E36" s="232"/>
-      <c r="F36" s="232"/>
-      <c r="G36" s="232"/>
-      <c r="H36" s="232"/>
-      <c r="I36" s="232"/>
-      <c r="J36" s="232"/>
-      <c r="K36" s="232"/>
-      <c r="L36" s="232"/>
-      <c r="M36" s="232"/>
-      <c r="N36" s="232"/>
-      <c r="O36" s="233"/>
+      <c r="A36" s="197"/>
+      <c r="B36" s="198"/>
+      <c r="C36" s="199"/>
+      <c r="D36" s="199"/>
+      <c r="E36" s="199"/>
+      <c r="F36" s="199"/>
+      <c r="G36" s="199"/>
+      <c r="H36" s="199"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="199"/>
+      <c r="K36" s="199"/>
+      <c r="L36" s="199"/>
+      <c r="M36" s="199"/>
+      <c r="N36" s="199"/>
+      <c r="O36" s="200"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="256"/>
-      <c r="B37" s="257"/>
-      <c r="C37" s="232"/>
-      <c r="D37" s="232"/>
-      <c r="E37" s="232"/>
-      <c r="F37" s="232"/>
-      <c r="G37" s="232"/>
-      <c r="H37" s="232"/>
-      <c r="I37" s="232"/>
-      <c r="J37" s="232"/>
-      <c r="K37" s="232"/>
-      <c r="L37" s="232"/>
-      <c r="M37" s="232"/>
-      <c r="N37" s="232"/>
-      <c r="O37" s="233"/>
+      <c r="A37" s="197"/>
+      <c r="B37" s="198"/>
+      <c r="C37" s="199"/>
+      <c r="D37" s="199"/>
+      <c r="E37" s="199"/>
+      <c r="F37" s="199"/>
+      <c r="G37" s="199"/>
+      <c r="H37" s="199"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="199"/>
+      <c r="K37" s="199"/>
+      <c r="L37" s="199"/>
+      <c r="M37" s="199"/>
+      <c r="N37" s="199"/>
+      <c r="O37" s="200"/>
     </row>
     <row r="38" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="246"/>
-      <c r="B38" s="247"/>
-      <c r="C38" s="225"/>
-      <c r="D38" s="225"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
-      <c r="G38" s="225"/>
-      <c r="H38" s="225"/>
-      <c r="I38" s="225"/>
-      <c r="J38" s="225"/>
-      <c r="K38" s="225"/>
-      <c r="L38" s="225"/>
-      <c r="M38" s="225"/>
-      <c r="N38" s="225"/>
-      <c r="O38" s="226"/>
+      <c r="A38" s="201"/>
+      <c r="B38" s="202"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="203"/>
+      <c r="I38" s="203"/>
+      <c r="J38" s="203"/>
+      <c r="K38" s="203"/>
+      <c r="L38" s="203"/>
+      <c r="M38" s="203"/>
+      <c r="N38" s="203"/>
+      <c r="O38" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:O37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:O38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:O35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:O36"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:O23"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:O32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:O28"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:O31"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:O7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:O10"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:O19"/>
     <mergeCell ref="A20:B20"/>
@@ -17732,25 +17733,33 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:O16"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:O7"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:O32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:O27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:O28"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:O31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:O23"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:O37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:O38"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:O35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:O36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
